--- a/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -653,181 +653,193 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6807600</v>
+        <v>7843500</v>
       </c>
       <c r="E8" s="3">
-        <v>6778700</v>
+        <v>6910200</v>
       </c>
       <c r="F8" s="3">
-        <v>6448300</v>
+        <v>6880700</v>
       </c>
       <c r="G8" s="3">
-        <v>7683600</v>
+        <v>6545400</v>
       </c>
       <c r="H8" s="3">
-        <v>6614000</v>
+        <v>7799400</v>
       </c>
       <c r="I8" s="3">
-        <v>6632000</v>
+        <v>6713600</v>
       </c>
       <c r="J8" s="3">
+        <v>6731900</v>
+      </c>
+      <c r="K8" s="3">
         <v>5838900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6563900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6008300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6482200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6193500</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3606800</v>
+        <v>4149400</v>
       </c>
       <c r="E9" s="3">
-        <v>3559800</v>
+        <v>3661100</v>
       </c>
       <c r="F9" s="3">
-        <v>3433600</v>
+        <v>3613400</v>
       </c>
       <c r="G9" s="3">
-        <v>4241900</v>
+        <v>3485400</v>
       </c>
       <c r="H9" s="3">
-        <v>3619200</v>
+        <v>4305800</v>
       </c>
       <c r="I9" s="3">
-        <v>3550800</v>
+        <v>3673700</v>
       </c>
       <c r="J9" s="3">
+        <v>3604300</v>
+      </c>
+      <c r="K9" s="3">
         <v>3220100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3555900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3211100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3412700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3368400</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3200800</v>
+        <v>3694100</v>
       </c>
       <c r="E10" s="3">
-        <v>3218900</v>
+        <v>3249000</v>
       </c>
       <c r="F10" s="3">
-        <v>3014600</v>
+        <v>3267400</v>
       </c>
       <c r="G10" s="3">
-        <v>3441800</v>
+        <v>3060000</v>
       </c>
       <c r="H10" s="3">
-        <v>2994900</v>
+        <v>3493600</v>
       </c>
       <c r="I10" s="3">
-        <v>3081200</v>
+        <v>3040000</v>
       </c>
       <c r="J10" s="3">
+        <v>3127600</v>
+      </c>
+      <c r="K10" s="3">
         <v>2618800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3008000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2797200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3069500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -842,46 +854,50 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>559900</v>
+        <v>573500</v>
       </c>
       <c r="E12" s="3">
-        <v>571100</v>
+        <v>568400</v>
       </c>
       <c r="F12" s="3">
-        <v>507900</v>
+        <v>579700</v>
       </c>
       <c r="G12" s="3">
-        <v>568800</v>
+        <v>515600</v>
       </c>
       <c r="H12" s="3">
-        <v>498100</v>
+        <v>577300</v>
       </c>
       <c r="I12" s="3">
-        <v>496100</v>
+        <v>505600</v>
       </c>
       <c r="J12" s="3">
+        <v>503600</v>
+      </c>
+      <c r="K12" s="3">
         <v>473700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>524400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>524200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>521500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,8 +934,11 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -956,8 +975,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -994,8 +1016,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1007,84 +1032,91 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>6259000</v>
+        <v>7061700</v>
       </c>
       <c r="E17" s="3">
-        <v>6166000</v>
+        <v>6353300</v>
       </c>
       <c r="F17" s="3">
-        <v>5887400</v>
+        <v>6258800</v>
       </c>
       <c r="G17" s="3">
-        <v>7037300</v>
+        <v>5976000</v>
       </c>
       <c r="H17" s="3">
-        <v>6073300</v>
+        <v>7143300</v>
       </c>
       <c r="I17" s="3">
-        <v>5978200</v>
+        <v>6164700</v>
       </c>
       <c r="J17" s="3">
+        <v>6068200</v>
+      </c>
+      <c r="K17" s="3">
         <v>5333300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6046200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5584800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5914300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5674800</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>548600</v>
+        <v>781800</v>
       </c>
       <c r="E18" s="3">
-        <v>612700</v>
+        <v>556900</v>
       </c>
       <c r="F18" s="3">
-        <v>560900</v>
+        <v>621900</v>
       </c>
       <c r="G18" s="3">
-        <v>646400</v>
+        <v>569400</v>
       </c>
       <c r="H18" s="3">
-        <v>540800</v>
+        <v>656100</v>
       </c>
       <c r="I18" s="3">
-        <v>653900</v>
+        <v>548900</v>
       </c>
       <c r="J18" s="3">
+        <v>663700</v>
+      </c>
+      <c r="K18" s="3">
         <v>505600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>517700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>423400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>567900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>518600</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1099,198 +1131,214 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>35600</v>
+        <v>-2800</v>
       </c>
       <c r="E20" s="3">
-        <v>62000</v>
+        <v>36100</v>
       </c>
       <c r="F20" s="3">
-        <v>22500</v>
+        <v>62900</v>
       </c>
       <c r="G20" s="3">
-        <v>155600</v>
+        <v>22800</v>
       </c>
       <c r="H20" s="3">
-        <v>-14300</v>
+        <v>158000</v>
       </c>
       <c r="I20" s="3">
-        <v>-86200</v>
+        <v>-14500</v>
       </c>
       <c r="J20" s="3">
+        <v>-87500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-54500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-24700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>149200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>63800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1001900</v>
+        <v>1214200</v>
       </c>
       <c r="E21" s="3">
-        <v>1064600</v>
+        <v>1017000</v>
       </c>
       <c r="F21" s="3">
-        <v>931800</v>
+        <v>1080700</v>
       </c>
       <c r="G21" s="3">
-        <v>1202200</v>
+        <v>945900</v>
       </c>
       <c r="H21" s="3">
-        <v>892500</v>
+        <v>1220300</v>
       </c>
       <c r="I21" s="3">
-        <v>944500</v>
+        <v>905900</v>
       </c>
       <c r="J21" s="3">
+        <v>958700</v>
+      </c>
+      <c r="K21" s="3">
         <v>811900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>904400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>964800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1044000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>860700</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E22" s="3">
         <v>4400</v>
       </c>
-      <c r="E22" s="3">
-        <v>3200</v>
-      </c>
       <c r="F22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G22" s="3">
         <v>2200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>579800</v>
+        <v>773700</v>
       </c>
       <c r="E23" s="3">
-        <v>671500</v>
+        <v>588500</v>
       </c>
       <c r="F23" s="3">
-        <v>581200</v>
+        <v>681600</v>
       </c>
       <c r="G23" s="3">
-        <v>799900</v>
+        <v>590000</v>
       </c>
       <c r="H23" s="3">
-        <v>525100</v>
+        <v>812000</v>
       </c>
       <c r="I23" s="3">
-        <v>565700</v>
+        <v>533000</v>
       </c>
       <c r="J23" s="3">
+        <v>574200</v>
+      </c>
+      <c r="K23" s="3">
         <v>449500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>491600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>571900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>630400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>142000</v>
+        <v>191400</v>
       </c>
       <c r="E24" s="3">
-        <v>204300</v>
+        <v>144100</v>
       </c>
       <c r="F24" s="3">
-        <v>171300</v>
+        <v>207400</v>
       </c>
       <c r="G24" s="3">
-        <v>201800</v>
+        <v>173900</v>
       </c>
       <c r="H24" s="3">
-        <v>144900</v>
+        <v>204900</v>
       </c>
       <c r="I24" s="3">
-        <v>147600</v>
+        <v>147100</v>
       </c>
       <c r="J24" s="3">
+        <v>149800</v>
+      </c>
+      <c r="K24" s="3">
         <v>118900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>55900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>180300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>156200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>128500</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1327,84 +1375,93 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>437800</v>
+        <v>582300</v>
       </c>
       <c r="E26" s="3">
-        <v>467200</v>
+        <v>444400</v>
       </c>
       <c r="F26" s="3">
-        <v>409900</v>
+        <v>474200</v>
       </c>
       <c r="G26" s="3">
-        <v>598100</v>
+        <v>416100</v>
       </c>
       <c r="H26" s="3">
-        <v>380100</v>
+        <v>607100</v>
       </c>
       <c r="I26" s="3">
-        <v>418100</v>
+        <v>385900</v>
       </c>
       <c r="J26" s="3">
+        <v>424400</v>
+      </c>
+      <c r="K26" s="3">
         <v>330600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>435700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>391700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>474200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>412600</v>
+        <v>543000</v>
       </c>
       <c r="E27" s="3">
-        <v>434300</v>
+        <v>418800</v>
       </c>
       <c r="F27" s="3">
-        <v>374600</v>
+        <v>440800</v>
       </c>
       <c r="G27" s="3">
-        <v>563400</v>
+        <v>380200</v>
       </c>
       <c r="H27" s="3">
-        <v>359300</v>
+        <v>571800</v>
       </c>
       <c r="I27" s="3">
-        <v>391900</v>
+        <v>364800</v>
       </c>
       <c r="J27" s="3">
+        <v>397800</v>
+      </c>
+      <c r="K27" s="3">
         <v>305300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>410800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>355600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>449400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1441,8 +1498,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1479,8 +1539,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1517,8 +1580,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1555,84 +1621,93 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-35600</v>
+        <v>2800</v>
       </c>
       <c r="E32" s="3">
-        <v>-62000</v>
+        <v>-36100</v>
       </c>
       <c r="F32" s="3">
-        <v>-22500</v>
+        <v>-62900</v>
       </c>
       <c r="G32" s="3">
-        <v>-155600</v>
+        <v>-22800</v>
       </c>
       <c r="H32" s="3">
-        <v>14300</v>
+        <v>-158000</v>
       </c>
       <c r="I32" s="3">
-        <v>86200</v>
+        <v>14500</v>
       </c>
       <c r="J32" s="3">
+        <v>87500</v>
+      </c>
+      <c r="K32" s="3">
         <v>54500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>24700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-149200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-63800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>412600</v>
+        <v>543000</v>
       </c>
       <c r="E33" s="3">
-        <v>434300</v>
+        <v>418800</v>
       </c>
       <c r="F33" s="3">
-        <v>374600</v>
+        <v>440800</v>
       </c>
       <c r="G33" s="3">
-        <v>563400</v>
+        <v>380200</v>
       </c>
       <c r="H33" s="3">
-        <v>359300</v>
+        <v>571800</v>
       </c>
       <c r="I33" s="3">
-        <v>391900</v>
+        <v>364800</v>
       </c>
       <c r="J33" s="3">
+        <v>397800</v>
+      </c>
+      <c r="K33" s="3">
         <v>305300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>410800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>355600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>449400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1669,89 +1744,98 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>412600</v>
+        <v>543000</v>
       </c>
       <c r="E35" s="3">
-        <v>434300</v>
+        <v>418800</v>
       </c>
       <c r="F35" s="3">
-        <v>374600</v>
+        <v>440800</v>
       </c>
       <c r="G35" s="3">
-        <v>563400</v>
+        <v>380200</v>
       </c>
       <c r="H35" s="3">
-        <v>359300</v>
+        <v>571800</v>
       </c>
       <c r="I35" s="3">
-        <v>391900</v>
+        <v>364800</v>
       </c>
       <c r="J35" s="3">
+        <v>397800</v>
+      </c>
+      <c r="K35" s="3">
         <v>305300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>410800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>355600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>449400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1766,8 +1850,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1782,75 +1867,79 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>3457700</v>
+        <v>2704900</v>
       </c>
       <c r="E41" s="3">
-        <v>3600300</v>
+        <v>3509800</v>
       </c>
       <c r="F41" s="3">
-        <v>3171900</v>
+        <v>3654500</v>
       </c>
       <c r="G41" s="3">
-        <v>2404400</v>
+        <v>3219700</v>
       </c>
       <c r="H41" s="3">
-        <v>3089600</v>
+        <v>2440600</v>
       </c>
       <c r="I41" s="3">
-        <v>3016700</v>
+        <v>3136100</v>
       </c>
       <c r="J41" s="3">
+        <v>3062100</v>
+      </c>
+      <c r="K41" s="3">
         <v>2870900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2757600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3477000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3848200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3553000</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>28700</v>
+        <v>25800</v>
       </c>
       <c r="E42" s="3">
-        <v>20400</v>
+        <v>29100</v>
       </c>
       <c r="F42" s="3">
-        <v>52300</v>
+        <v>20700</v>
       </c>
       <c r="G42" s="3">
-        <v>72400</v>
+        <v>53100</v>
       </c>
       <c r="H42" s="3">
-        <v>81100</v>
+        <v>73500</v>
       </c>
       <c r="I42" s="3">
-        <v>56700</v>
+        <v>82300</v>
       </c>
       <c r="J42" s="3">
+        <v>57600</v>
+      </c>
+      <c r="K42" s="3">
         <v>26600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>23200</v>
-      </c>
-      <c r="L42" s="3">
-        <v>700</v>
       </c>
       <c r="M42" s="3">
         <v>700</v>
@@ -1858,274 +1947,298 @@
       <c r="N42" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>5086100</v>
+        <v>5327700</v>
       </c>
       <c r="E43" s="3">
-        <v>4985200</v>
+        <v>5162700</v>
       </c>
       <c r="F43" s="3">
-        <v>4775300</v>
+        <v>5060300</v>
       </c>
       <c r="G43" s="3">
-        <v>5037100</v>
+        <v>4847200</v>
       </c>
       <c r="H43" s="3">
-        <v>3697700</v>
+        <v>5113000</v>
       </c>
       <c r="I43" s="3">
-        <v>3659600</v>
+        <v>3753400</v>
       </c>
       <c r="J43" s="3">
+        <v>3714700</v>
+      </c>
+      <c r="K43" s="3">
         <v>3497900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3493500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3275800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3533700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3740600</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>6068100</v>
+        <v>5371000</v>
       </c>
       <c r="E44" s="3">
-        <v>5963600</v>
+        <v>6159500</v>
       </c>
       <c r="F44" s="3">
-        <v>5702600</v>
+        <v>6053400</v>
       </c>
       <c r="G44" s="3">
-        <v>5367200</v>
+        <v>5788500</v>
       </c>
       <c r="H44" s="3">
-        <v>5869100</v>
+        <v>5448000</v>
       </c>
       <c r="I44" s="3">
-        <v>5299600</v>
+        <v>5957500</v>
       </c>
       <c r="J44" s="3">
+        <v>5379400</v>
+      </c>
+      <c r="K44" s="3">
         <v>4868500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4469400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4587800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4330100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4379900</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>1702700</v>
+        <v>1561000</v>
       </c>
       <c r="E45" s="3">
-        <v>1671200</v>
+        <v>1728300</v>
       </c>
       <c r="F45" s="3">
-        <v>1381200</v>
+        <v>1696400</v>
       </c>
       <c r="G45" s="3">
-        <v>1434200</v>
+        <v>1402000</v>
       </c>
       <c r="H45" s="3">
-        <v>2498600</v>
+        <v>1455800</v>
       </c>
       <c r="I45" s="3">
-        <v>2401200</v>
+        <v>2536200</v>
       </c>
       <c r="J45" s="3">
+        <v>2437300</v>
+      </c>
+      <c r="K45" s="3">
         <v>2133500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2160500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2308900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2275900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2209100</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>16343300</v>
+        <v>14990300</v>
       </c>
       <c r="E46" s="3">
-        <v>16240600</v>
+        <v>16589500</v>
       </c>
       <c r="F46" s="3">
-        <v>15083300</v>
+        <v>16485200</v>
       </c>
       <c r="G46" s="3">
-        <v>14315300</v>
+        <v>15310400</v>
       </c>
       <c r="H46" s="3">
-        <v>15236100</v>
+        <v>14530900</v>
       </c>
       <c r="I46" s="3">
-        <v>14433800</v>
+        <v>15465500</v>
       </c>
       <c r="J46" s="3">
+        <v>14651200</v>
+      </c>
+      <c r="K46" s="3">
         <v>13397400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12904200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13650100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13988700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13883200</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2695000</v>
+        <v>2746500</v>
       </c>
       <c r="E47" s="3">
-        <v>2736800</v>
+        <v>2735600</v>
       </c>
       <c r="F47" s="3">
-        <v>2449600</v>
+        <v>2778000</v>
       </c>
       <c r="G47" s="3">
-        <v>2349200</v>
+        <v>2486500</v>
       </c>
       <c r="H47" s="3">
-        <v>469000</v>
+        <v>2384500</v>
       </c>
       <c r="I47" s="3">
-        <v>470000</v>
+        <v>476100</v>
       </c>
       <c r="J47" s="3">
+        <v>477100</v>
+      </c>
+      <c r="K47" s="3">
         <v>481600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>515200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>556100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>509400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>497200</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>8136200</v>
+        <v>8236300</v>
       </c>
       <c r="E48" s="3">
-        <v>8131500</v>
+        <v>8258700</v>
       </c>
       <c r="F48" s="3">
-        <v>7779000</v>
+        <v>8254000</v>
       </c>
       <c r="G48" s="3">
-        <v>7655300</v>
+        <v>7896200</v>
       </c>
       <c r="H48" s="3">
-        <v>7745800</v>
+        <v>7770600</v>
       </c>
       <c r="I48" s="3">
-        <v>7733100</v>
+        <v>7862500</v>
       </c>
       <c r="J48" s="3">
+        <v>7849600</v>
+      </c>
+      <c r="K48" s="3">
         <v>7659100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7812500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8166000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8367100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8429500</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>8711800</v>
+        <v>8899100</v>
       </c>
       <c r="E49" s="3">
-        <v>8524200</v>
+        <v>8843000</v>
       </c>
       <c r="F49" s="3">
-        <v>8327600</v>
+        <v>8652600</v>
       </c>
       <c r="G49" s="3">
-        <v>8324000</v>
+        <v>8453000</v>
       </c>
       <c r="H49" s="3">
-        <v>8503600</v>
+        <v>8449400</v>
       </c>
       <c r="I49" s="3">
-        <v>8548300</v>
+        <v>8631600</v>
       </c>
       <c r="J49" s="3">
+        <v>8677100</v>
+      </c>
+      <c r="K49" s="3">
         <v>8466100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8626300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9054200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9078800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9087100</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2162,8 +2275,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2200,46 +2316,52 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1423900</v>
+        <v>1635500</v>
       </c>
       <c r="E52" s="3">
-        <v>1360400</v>
+        <v>1445300</v>
       </c>
       <c r="F52" s="3">
-        <v>1278600</v>
+        <v>1380800</v>
       </c>
       <c r="G52" s="3">
-        <v>1190500</v>
+        <v>1297800</v>
       </c>
       <c r="H52" s="3">
-        <v>3244500</v>
+        <v>1208500</v>
       </c>
       <c r="I52" s="3">
-        <v>3038300</v>
+        <v>3293400</v>
       </c>
       <c r="J52" s="3">
+        <v>3084000</v>
+      </c>
+      <c r="K52" s="3">
         <v>2829500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2780400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2837000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2948300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2900900</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2276,46 +2398,52 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>37310200</v>
+        <v>36507700</v>
       </c>
       <c r="E54" s="3">
-        <v>36993500</v>
+        <v>37872100</v>
       </c>
       <c r="F54" s="3">
-        <v>34918000</v>
+        <v>37550600</v>
       </c>
       <c r="G54" s="3">
-        <v>33834300</v>
+        <v>35443900</v>
       </c>
       <c r="H54" s="3">
-        <v>35199000</v>
+        <v>34343900</v>
       </c>
       <c r="I54" s="3">
-        <v>34223500</v>
+        <v>35729100</v>
       </c>
       <c r="J54" s="3">
+        <v>34738900</v>
+      </c>
+      <c r="K54" s="3">
         <v>32833600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32638600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34263500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34892400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34797900</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2330,8 +2458,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2346,236 +2475,255 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2284600</v>
+        <v>2088900</v>
       </c>
       <c r="E57" s="3">
-        <v>2393700</v>
+        <v>2319000</v>
       </c>
       <c r="F57" s="3">
-        <v>2420500</v>
+        <v>2429800</v>
       </c>
       <c r="G57" s="3">
+        <v>2456900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2399000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>2648800</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2467100</v>
+      </c>
+      <c r="K57" s="3">
+        <v>2333300</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2326200</v>
+      </c>
+      <c r="M57" s="3">
         <v>2363400</v>
       </c>
-      <c r="H57" s="3">
-        <v>2609500</v>
-      </c>
-      <c r="I57" s="3">
-        <v>2430500</v>
-      </c>
-      <c r="J57" s="3">
-        <v>2333300</v>
-      </c>
-      <c r="K57" s="3">
-        <v>2326200</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2363400</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2294200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2332900</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>4034300</v>
+        <v>2603000</v>
       </c>
       <c r="E58" s="3">
-        <v>3563900</v>
+        <v>4095000</v>
       </c>
       <c r="F58" s="3">
-        <v>2900300</v>
+        <v>3617600</v>
       </c>
       <c r="G58" s="3">
-        <v>1968000</v>
+        <v>2944000</v>
       </c>
       <c r="H58" s="3">
-        <v>1612100</v>
+        <v>1997600</v>
       </c>
       <c r="I58" s="3">
-        <v>894000</v>
+        <v>1636400</v>
       </c>
       <c r="J58" s="3">
+        <v>907400</v>
+      </c>
+      <c r="K58" s="3">
         <v>963500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>308400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2493700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2540900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3014200</v>
       </c>
     </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>5137200</v>
+        <v>5008100</v>
       </c>
       <c r="E59" s="3">
-        <v>4987000</v>
+        <v>5214600</v>
       </c>
       <c r="F59" s="3">
-        <v>4694200</v>
+        <v>5062100</v>
       </c>
       <c r="G59" s="3">
-        <v>4734600</v>
+        <v>4764900</v>
       </c>
       <c r="H59" s="3">
-        <v>4672300</v>
+        <v>4805900</v>
       </c>
       <c r="I59" s="3">
-        <v>4502900</v>
+        <v>4742700</v>
       </c>
       <c r="J59" s="3">
+        <v>4570700</v>
+      </c>
+      <c r="K59" s="3">
         <v>4265600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4653300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4839300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4883300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4769000</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>11456100</v>
+        <v>9700000</v>
       </c>
       <c r="E60" s="3">
-        <v>10944600</v>
+        <v>11628600</v>
       </c>
       <c r="F60" s="3">
-        <v>10015000</v>
+        <v>11109500</v>
       </c>
       <c r="G60" s="3">
-        <v>9065900</v>
+        <v>10165800</v>
       </c>
       <c r="H60" s="3">
-        <v>8894000</v>
+        <v>9202500</v>
       </c>
       <c r="I60" s="3">
-        <v>7827300</v>
+        <v>9027900</v>
       </c>
       <c r="J60" s="3">
+        <v>7945200</v>
+      </c>
+      <c r="K60" s="3">
         <v>7562300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7287900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9696400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9718400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10116000</v>
       </c>
     </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>19400</v>
+        <v>19900</v>
       </c>
       <c r="E61" s="3">
-        <v>16100</v>
+        <v>19700</v>
       </c>
       <c r="F61" s="3">
-        <v>15700</v>
+        <v>16400</v>
       </c>
       <c r="G61" s="3">
-        <v>16000</v>
+        <v>15900</v>
       </c>
       <c r="H61" s="3">
-        <v>1197300</v>
+        <v>16300</v>
       </c>
       <c r="I61" s="3">
-        <v>1197500</v>
+        <v>1215300</v>
       </c>
       <c r="J61" s="3">
+        <v>1215500</v>
+      </c>
+      <c r="K61" s="3">
         <v>1192900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1234900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>42700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>41700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>2359000</v>
+        <v>2485300</v>
       </c>
       <c r="E62" s="3">
-        <v>2493500</v>
+        <v>2394500</v>
       </c>
       <c r="F62" s="3">
-        <v>2439700</v>
+        <v>2531100</v>
       </c>
       <c r="G62" s="3">
-        <v>2514800</v>
+        <v>2476400</v>
       </c>
       <c r="H62" s="3">
-        <v>2835700</v>
+        <v>2552600</v>
       </c>
       <c r="I62" s="3">
-        <v>2863400</v>
+        <v>2878400</v>
       </c>
       <c r="J62" s="3">
+        <v>2906500</v>
+      </c>
+      <c r="K62" s="3">
         <v>2842100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2829600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3188900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3366400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3458200</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2612,8 +2760,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2650,8 +2801,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2688,46 +2842,52 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>15456600</v>
+        <v>13908400</v>
       </c>
       <c r="E66" s="3">
-        <v>15072500</v>
+        <v>15689400</v>
       </c>
       <c r="F66" s="3">
-        <v>14051300</v>
+        <v>15299500</v>
       </c>
       <c r="G66" s="3">
-        <v>13163300</v>
+        <v>14262900</v>
       </c>
       <c r="H66" s="3">
-        <v>14464800</v>
+        <v>13361500</v>
       </c>
       <c r="I66" s="3">
-        <v>13418200</v>
+        <v>14682600</v>
       </c>
       <c r="J66" s="3">
+        <v>13620300</v>
+      </c>
+      <c r="K66" s="3">
         <v>13099800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>12895800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14507600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14713500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15171700</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2742,8 +2902,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2780,8 +2941,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2818,8 +2982,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2856,8 +3023,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2894,46 +3064,52 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>25114300</v>
+        <v>26035600</v>
       </c>
       <c r="E72" s="3">
-        <v>25166200</v>
+        <v>25492600</v>
       </c>
       <c r="F72" s="3">
-        <v>24732200</v>
+        <v>25545200</v>
       </c>
       <c r="G72" s="3">
-        <v>24762200</v>
+        <v>25104600</v>
       </c>
       <c r="H72" s="3">
-        <v>24198800</v>
+        <v>25135100</v>
       </c>
       <c r="I72" s="3">
-        <v>24249900</v>
+        <v>24563300</v>
       </c>
       <c r="J72" s="3">
+        <v>24615100</v>
+      </c>
+      <c r="K72" s="3">
         <v>23858000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>24773600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>25558200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>26037900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>25588500</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2970,8 +3146,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3008,8 +3187,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3046,46 +3228,52 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>21853600</v>
+        <v>22599400</v>
       </c>
       <c r="E76" s="3">
-        <v>21921000</v>
+        <v>22182700</v>
       </c>
       <c r="F76" s="3">
-        <v>20866700</v>
+        <v>22251100</v>
       </c>
       <c r="G76" s="3">
-        <v>20671000</v>
+        <v>21181000</v>
       </c>
       <c r="H76" s="3">
-        <v>20734300</v>
+        <v>20982300</v>
       </c>
       <c r="I76" s="3">
-        <v>20805300</v>
+        <v>21046500</v>
       </c>
       <c r="J76" s="3">
+        <v>21118600</v>
+      </c>
+      <c r="K76" s="3">
         <v>19733900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19742800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19755900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20178900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19626200</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3122,89 +3310,98 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>412600</v>
+        <v>543000</v>
       </c>
       <c r="E81" s="3">
-        <v>434300</v>
+        <v>418800</v>
       </c>
       <c r="F81" s="3">
-        <v>374600</v>
+        <v>440800</v>
       </c>
       <c r="G81" s="3">
-        <v>563400</v>
+        <v>380200</v>
       </c>
       <c r="H81" s="3">
-        <v>359300</v>
+        <v>571800</v>
       </c>
       <c r="I81" s="3">
-        <v>391900</v>
+        <v>364800</v>
       </c>
       <c r="J81" s="3">
+        <v>397800</v>
+      </c>
+      <c r="K81" s="3">
         <v>305300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>410800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>355600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>449400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3219,46 +3416,50 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>417800</v>
+        <v>435200</v>
       </c>
       <c r="E83" s="3">
-        <v>389900</v>
+        <v>424100</v>
       </c>
       <c r="F83" s="3">
-        <v>348400</v>
+        <v>395800</v>
       </c>
       <c r="G83" s="3">
-        <v>400200</v>
+        <v>353700</v>
       </c>
       <c r="H83" s="3">
-        <v>366000</v>
+        <v>406200</v>
       </c>
       <c r="I83" s="3">
-        <v>376800</v>
+        <v>371500</v>
       </c>
       <c r="J83" s="3">
+        <v>382500</v>
+      </c>
+      <c r="K83" s="3">
         <v>360900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>411300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>392200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>412300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>374000</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3295,8 +3496,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3333,8 +3537,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3371,8 +3578,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3409,8 +3619,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3447,46 +3660,52 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>769100</v>
+        <v>1222000</v>
       </c>
       <c r="E89" s="3">
-        <v>534200</v>
+        <v>780700</v>
       </c>
       <c r="F89" s="3">
-        <v>488800</v>
+        <v>542200</v>
       </c>
       <c r="G89" s="3">
-        <v>492200</v>
+        <v>496100</v>
       </c>
       <c r="H89" s="3">
-        <v>397700</v>
+        <v>499600</v>
       </c>
       <c r="I89" s="3">
-        <v>751300</v>
+        <v>403700</v>
       </c>
       <c r="J89" s="3">
+        <v>762700</v>
+      </c>
+      <c r="K89" s="3">
         <v>102400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>694300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>557800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1053700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>950000</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3501,46 +3720,50 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-73360000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-66263000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-47371000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-43314000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-56276000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-44602000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-40183000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47466000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-54255000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41155000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-299600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-302700</v>
       </c>
     </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3577,8 +3800,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3615,46 +3841,52 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-728100</v>
+        <v>-480900</v>
       </c>
       <c r="E94" s="3">
-        <v>-373500</v>
+        <v>-739100</v>
       </c>
       <c r="F94" s="3">
-        <v>-253100</v>
+        <v>-379100</v>
       </c>
       <c r="G94" s="3">
-        <v>-321800</v>
+        <v>-257000</v>
       </c>
       <c r="H94" s="3">
-        <v>-325100</v>
+        <v>-326700</v>
       </c>
       <c r="I94" s="3">
-        <v>-321000</v>
+        <v>-330000</v>
       </c>
       <c r="J94" s="3">
+        <v>-325800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-232700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-404700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-490000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-302300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-288600</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3669,46 +3901,50 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-464400</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-471400</v>
       </c>
       <c r="F96" s="3">
-        <v>-404600</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-410700</v>
       </c>
       <c r="H96" s="3">
-        <v>-410400</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-416600</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-381900</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-339300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3745,8 +3981,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3783,8 +4022,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3821,118 +4063,130 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-223100</v>
+        <v>-1495000</v>
       </c>
       <c r="E100" s="3">
-        <v>152300</v>
+        <v>-226400</v>
       </c>
       <c r="F100" s="3">
-        <v>502900</v>
+        <v>154600</v>
       </c>
       <c r="G100" s="3">
-        <v>-778600</v>
+        <v>510400</v>
       </c>
       <c r="H100" s="3">
-        <v>-47000</v>
+        <v>-790300</v>
       </c>
       <c r="I100" s="3">
-        <v>-403300</v>
+        <v>-47700</v>
       </c>
       <c r="J100" s="3">
+        <v>-409400</v>
+      </c>
+      <c r="K100" s="3">
         <v>253800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-875100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-362500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-469900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-189500</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>39500</v>
+        <v>-51000</v>
       </c>
       <c r="E101" s="3">
-        <v>115300</v>
+        <v>40100</v>
       </c>
       <c r="F101" s="3">
-        <v>29100</v>
+        <v>117000</v>
       </c>
       <c r="G101" s="3">
-        <v>-76900</v>
+        <v>29500</v>
       </c>
       <c r="H101" s="3">
-        <v>47200</v>
+        <v>-78100</v>
       </c>
       <c r="I101" s="3">
-        <v>118800</v>
+        <v>47900</v>
       </c>
       <c r="J101" s="3">
+        <v>120600</v>
+      </c>
+      <c r="K101" s="3">
         <v>82100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>30100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>13700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>84700</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-142500</v>
+        <v>-804900</v>
       </c>
       <c r="E102" s="3">
-        <v>428300</v>
+        <v>-144700</v>
       </c>
       <c r="F102" s="3">
-        <v>767600</v>
+        <v>434800</v>
       </c>
       <c r="G102" s="3">
-        <v>-685200</v>
+        <v>779100</v>
       </c>
       <c r="H102" s="3">
-        <v>72900</v>
+        <v>-695500</v>
       </c>
       <c r="I102" s="3">
-        <v>145800</v>
+        <v>74000</v>
       </c>
       <c r="J102" s="3">
+        <v>148000</v>
+      </c>
+      <c r="K102" s="3">
         <v>205600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-555400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-298000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>295200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>556500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
@@ -653,193 +653,205 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7843500</v>
+        <v>6306800</v>
       </c>
       <c r="E8" s="3">
-        <v>6910200</v>
+        <v>7424500</v>
       </c>
       <c r="F8" s="3">
-        <v>6880700</v>
+        <v>6541100</v>
       </c>
       <c r="G8" s="3">
-        <v>6545400</v>
+        <v>6513200</v>
       </c>
       <c r="H8" s="3">
-        <v>7799400</v>
+        <v>6195800</v>
       </c>
       <c r="I8" s="3">
-        <v>6713600</v>
+        <v>7382800</v>
       </c>
       <c r="J8" s="3">
+        <v>6355100</v>
+      </c>
+      <c r="K8" s="3">
         <v>6731900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5838900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6563900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6008300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6482200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6193500</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4149400</v>
+        <v>3254300</v>
       </c>
       <c r="E9" s="3">
-        <v>3661100</v>
+        <v>3927800</v>
       </c>
       <c r="F9" s="3">
-        <v>3613400</v>
+        <v>3465600</v>
       </c>
       <c r="G9" s="3">
-        <v>3485400</v>
+        <v>3420400</v>
       </c>
       <c r="H9" s="3">
-        <v>4305800</v>
+        <v>3299200</v>
       </c>
       <c r="I9" s="3">
-        <v>3673700</v>
+        <v>4075800</v>
       </c>
       <c r="J9" s="3">
+        <v>3477500</v>
+      </c>
+      <c r="K9" s="3">
         <v>3604300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3220100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3555900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3211100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3412700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3368400</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3694100</v>
+        <v>3052500</v>
       </c>
       <c r="E10" s="3">
-        <v>3249000</v>
+        <v>3496700</v>
       </c>
       <c r="F10" s="3">
-        <v>3267400</v>
+        <v>3075500</v>
       </c>
       <c r="G10" s="3">
-        <v>3060000</v>
+        <v>3092800</v>
       </c>
       <c r="H10" s="3">
-        <v>3493600</v>
+        <v>2896600</v>
       </c>
       <c r="I10" s="3">
-        <v>3040000</v>
+        <v>3307000</v>
       </c>
       <c r="J10" s="3">
+        <v>2877600</v>
+      </c>
+      <c r="K10" s="3">
         <v>3127600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2618800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3008000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2797200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3069500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -855,49 +867,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>573500</v>
+        <v>506900</v>
       </c>
       <c r="E12" s="3">
-        <v>568400</v>
+        <v>542800</v>
       </c>
       <c r="F12" s="3">
-        <v>579700</v>
+        <v>538000</v>
       </c>
       <c r="G12" s="3">
-        <v>515600</v>
+        <v>548700</v>
       </c>
       <c r="H12" s="3">
-        <v>577300</v>
+        <v>488100</v>
       </c>
       <c r="I12" s="3">
-        <v>505600</v>
+        <v>546500</v>
       </c>
       <c r="J12" s="3">
+        <v>478600</v>
+      </c>
+      <c r="K12" s="3">
         <v>503600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>473700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>524400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>524200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>521500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -937,8 +953,11 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -978,8 +997,11 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1019,8 +1041,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1033,90 +1058,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>7061700</v>
+        <v>5795800</v>
       </c>
       <c r="E17" s="3">
-        <v>6353300</v>
+        <v>6684500</v>
       </c>
       <c r="F17" s="3">
-        <v>6258800</v>
+        <v>6013900</v>
       </c>
       <c r="G17" s="3">
-        <v>5976000</v>
+        <v>5924500</v>
       </c>
       <c r="H17" s="3">
-        <v>7143300</v>
+        <v>5656800</v>
       </c>
       <c r="I17" s="3">
-        <v>6164700</v>
+        <v>6761700</v>
       </c>
       <c r="J17" s="3">
+        <v>5835500</v>
+      </c>
+      <c r="K17" s="3">
         <v>6068200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5333300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6046200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5584800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5914300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5674800</v>
       </c>
     </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>781800</v>
+        <v>510900</v>
       </c>
       <c r="E18" s="3">
-        <v>556900</v>
+        <v>740000</v>
       </c>
       <c r="F18" s="3">
-        <v>621900</v>
+        <v>527100</v>
       </c>
       <c r="G18" s="3">
-        <v>569400</v>
+        <v>588700</v>
       </c>
       <c r="H18" s="3">
-        <v>656100</v>
+        <v>539000</v>
       </c>
       <c r="I18" s="3">
-        <v>548900</v>
+        <v>621100</v>
       </c>
       <c r="J18" s="3">
+        <v>519600</v>
+      </c>
+      <c r="K18" s="3">
         <v>663700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>505600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>517700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>423400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>567900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>518600</v>
       </c>
     </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1132,213 +1164,229 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-2800</v>
+        <v>62300</v>
       </c>
       <c r="E20" s="3">
-        <v>36100</v>
+        <v>-2600</v>
       </c>
       <c r="F20" s="3">
-        <v>62900</v>
+        <v>34200</v>
       </c>
       <c r="G20" s="3">
-        <v>22800</v>
+        <v>59600</v>
       </c>
       <c r="H20" s="3">
-        <v>158000</v>
+        <v>21600</v>
       </c>
       <c r="I20" s="3">
-        <v>-14500</v>
+        <v>149500</v>
       </c>
       <c r="J20" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="K20" s="3">
         <v>-87500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-54500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>149200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>63800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1214200</v>
+        <v>920600</v>
       </c>
       <c r="E21" s="3">
-        <v>1017000</v>
+        <v>1149300</v>
       </c>
       <c r="F21" s="3">
-        <v>1080700</v>
+        <v>962700</v>
       </c>
       <c r="G21" s="3">
-        <v>945900</v>
+        <v>1023000</v>
       </c>
       <c r="H21" s="3">
-        <v>1220300</v>
+        <v>895300</v>
       </c>
       <c r="I21" s="3">
-        <v>905900</v>
+        <v>1155100</v>
       </c>
       <c r="J21" s="3">
+        <v>857500</v>
+      </c>
+      <c r="K21" s="3">
         <v>958700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>811900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>904400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>964800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1044000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>860700</v>
       </c>
     </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>5300</v>
+        <v>4000</v>
       </c>
       <c r="E22" s="3">
-        <v>4400</v>
+        <v>5100</v>
       </c>
       <c r="F22" s="3">
-        <v>3300</v>
+        <v>4200</v>
       </c>
       <c r="G22" s="3">
-        <v>2200</v>
+        <v>3100</v>
       </c>
       <c r="H22" s="3">
         <v>2100</v>
       </c>
       <c r="I22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K22" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>773700</v>
+        <v>569200</v>
       </c>
       <c r="E23" s="3">
-        <v>588500</v>
+        <v>732300</v>
       </c>
       <c r="F23" s="3">
-        <v>681600</v>
+        <v>557100</v>
       </c>
       <c r="G23" s="3">
-        <v>590000</v>
+        <v>645200</v>
       </c>
       <c r="H23" s="3">
-        <v>812000</v>
+        <v>558500</v>
       </c>
       <c r="I23" s="3">
-        <v>533000</v>
+        <v>768600</v>
       </c>
       <c r="J23" s="3">
+        <v>504500</v>
+      </c>
+      <c r="K23" s="3">
         <v>574200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>449500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>491600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>571900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>630400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>191400</v>
+        <v>159600</v>
       </c>
       <c r="E24" s="3">
-        <v>144100</v>
+        <v>181200</v>
       </c>
       <c r="F24" s="3">
-        <v>207400</v>
+        <v>136400</v>
       </c>
       <c r="G24" s="3">
-        <v>173900</v>
+        <v>196300</v>
       </c>
       <c r="H24" s="3">
-        <v>204900</v>
+        <v>164600</v>
       </c>
       <c r="I24" s="3">
-        <v>147100</v>
+        <v>193900</v>
       </c>
       <c r="J24" s="3">
+        <v>139300</v>
+      </c>
+      <c r="K24" s="3">
         <v>149800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>118900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>55900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>180300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>156200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>128500</v>
       </c>
     </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1378,90 +1426,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>582300</v>
+        <v>409600</v>
       </c>
       <c r="E26" s="3">
-        <v>444400</v>
+        <v>551200</v>
       </c>
       <c r="F26" s="3">
+        <v>420700</v>
+      </c>
+      <c r="G26" s="3">
+        <v>448900</v>
+      </c>
+      <c r="H26" s="3">
+        <v>393800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>574700</v>
+      </c>
+      <c r="J26" s="3">
+        <v>365200</v>
+      </c>
+      <c r="K26" s="3">
+        <v>424400</v>
+      </c>
+      <c r="L26" s="3">
+        <v>330600</v>
+      </c>
+      <c r="M26" s="3">
+        <v>435700</v>
+      </c>
+      <c r="N26" s="3">
+        <v>391700</v>
+      </c>
+      <c r="O26" s="3">
         <v>474200</v>
       </c>
-      <c r="G26" s="3">
-        <v>416100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>607100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>385900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>424400</v>
-      </c>
-      <c r="K26" s="3">
-        <v>330600</v>
-      </c>
-      <c r="L26" s="3">
-        <v>435700</v>
-      </c>
-      <c r="M26" s="3">
-        <v>391700</v>
-      </c>
-      <c r="N26" s="3">
-        <v>474200</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>543000</v>
+        <v>382500</v>
       </c>
       <c r="E27" s="3">
-        <v>418800</v>
+        <v>514000</v>
       </c>
       <c r="F27" s="3">
-        <v>440800</v>
+        <v>396400</v>
       </c>
       <c r="G27" s="3">
-        <v>380200</v>
+        <v>417300</v>
       </c>
       <c r="H27" s="3">
-        <v>571800</v>
+        <v>359900</v>
       </c>
       <c r="I27" s="3">
-        <v>364800</v>
+        <v>541300</v>
       </c>
       <c r="J27" s="3">
+        <v>345300</v>
+      </c>
+      <c r="K27" s="3">
         <v>397800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>305300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>410800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>355600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>449400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1501,8 +1558,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1542,8 +1602,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1583,8 +1646,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1624,90 +1690,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>2800</v>
+        <v>-62300</v>
       </c>
       <c r="E32" s="3">
-        <v>-36100</v>
+        <v>2600</v>
       </c>
       <c r="F32" s="3">
-        <v>-62900</v>
+        <v>-34200</v>
       </c>
       <c r="G32" s="3">
-        <v>-22800</v>
+        <v>-59600</v>
       </c>
       <c r="H32" s="3">
-        <v>-158000</v>
+        <v>-21600</v>
       </c>
       <c r="I32" s="3">
-        <v>14500</v>
+        <v>-149500</v>
       </c>
       <c r="J32" s="3">
+        <v>13800</v>
+      </c>
+      <c r="K32" s="3">
         <v>87500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>54500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-149200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-63800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>543000</v>
+        <v>382500</v>
       </c>
       <c r="E33" s="3">
-        <v>418800</v>
+        <v>514000</v>
       </c>
       <c r="F33" s="3">
-        <v>440800</v>
+        <v>396400</v>
       </c>
       <c r="G33" s="3">
-        <v>380200</v>
+        <v>417300</v>
       </c>
       <c r="H33" s="3">
-        <v>571800</v>
+        <v>359900</v>
       </c>
       <c r="I33" s="3">
-        <v>364800</v>
+        <v>541300</v>
       </c>
       <c r="J33" s="3">
+        <v>345300</v>
+      </c>
+      <c r="K33" s="3">
         <v>397800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>305300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>410800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>355600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>449400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1747,95 +1822,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>543000</v>
+        <v>382500</v>
       </c>
       <c r="E35" s="3">
-        <v>418800</v>
+        <v>514000</v>
       </c>
       <c r="F35" s="3">
-        <v>440800</v>
+        <v>396400</v>
       </c>
       <c r="G35" s="3">
-        <v>380200</v>
+        <v>417300</v>
       </c>
       <c r="H35" s="3">
-        <v>571800</v>
+        <v>359900</v>
       </c>
       <c r="I35" s="3">
-        <v>364800</v>
+        <v>541300</v>
       </c>
       <c r="J35" s="3">
+        <v>345300</v>
+      </c>
+      <c r="K35" s="3">
         <v>397800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>305300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>410800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>355600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>449400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1851,8 +1935,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1868,81 +1953,85 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>2704900</v>
+        <v>3250700</v>
       </c>
       <c r="E41" s="3">
-        <v>3509800</v>
+        <v>2560400</v>
       </c>
       <c r="F41" s="3">
-        <v>3654500</v>
+        <v>3322400</v>
       </c>
       <c r="G41" s="3">
-        <v>3219700</v>
+        <v>3459300</v>
       </c>
       <c r="H41" s="3">
-        <v>2440600</v>
+        <v>3047700</v>
       </c>
       <c r="I41" s="3">
-        <v>3136100</v>
+        <v>2310200</v>
       </c>
       <c r="J41" s="3">
+        <v>2968600</v>
+      </c>
+      <c r="K41" s="3">
         <v>3062100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2870900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2757600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3477000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3848200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3553000</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>25800</v>
+        <v>25100</v>
       </c>
       <c r="E42" s="3">
-        <v>29100</v>
+        <v>24400</v>
       </c>
       <c r="F42" s="3">
-        <v>20700</v>
+        <v>27600</v>
       </c>
       <c r="G42" s="3">
-        <v>53100</v>
+        <v>19600</v>
       </c>
       <c r="H42" s="3">
-        <v>73500</v>
+        <v>50200</v>
       </c>
       <c r="I42" s="3">
-        <v>82300</v>
+        <v>69600</v>
       </c>
       <c r="J42" s="3">
+        <v>77900</v>
+      </c>
+      <c r="K42" s="3">
         <v>57600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>26600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>23200</v>
-      </c>
-      <c r="M42" s="3">
-        <v>700</v>
       </c>
       <c r="N42" s="3">
         <v>700</v>
@@ -1950,295 +2039,319 @@
       <c r="O42" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>5327700</v>
+        <v>4979900</v>
       </c>
       <c r="E43" s="3">
-        <v>5162700</v>
+        <v>5043100</v>
       </c>
       <c r="F43" s="3">
-        <v>5060300</v>
+        <v>4887000</v>
       </c>
       <c r="G43" s="3">
-        <v>4847200</v>
+        <v>4790000</v>
       </c>
       <c r="H43" s="3">
-        <v>5113000</v>
+        <v>4588300</v>
       </c>
       <c r="I43" s="3">
-        <v>3753400</v>
+        <v>4839900</v>
       </c>
       <c r="J43" s="3">
+        <v>3552900</v>
+      </c>
+      <c r="K43" s="3">
         <v>3714700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3497900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3493500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3275800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3533700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3740600</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>5371000</v>
+        <v>5709300</v>
       </c>
       <c r="E44" s="3">
-        <v>6159500</v>
+        <v>5084100</v>
       </c>
       <c r="F44" s="3">
-        <v>6053400</v>
+        <v>5830500</v>
       </c>
       <c r="G44" s="3">
-        <v>5788500</v>
+        <v>5730000</v>
       </c>
       <c r="H44" s="3">
-        <v>5448000</v>
+        <v>5479300</v>
       </c>
       <c r="I44" s="3">
-        <v>5957500</v>
+        <v>5157000</v>
       </c>
       <c r="J44" s="3">
+        <v>5639300</v>
+      </c>
+      <c r="K44" s="3">
         <v>5379400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4868500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4469400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4587800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4330100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4379900</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>1561000</v>
+        <v>1564800</v>
       </c>
       <c r="E45" s="3">
-        <v>1728300</v>
+        <v>1477600</v>
       </c>
       <c r="F45" s="3">
-        <v>1696400</v>
+        <v>1636000</v>
       </c>
       <c r="G45" s="3">
-        <v>1402000</v>
+        <v>1605800</v>
       </c>
       <c r="H45" s="3">
-        <v>1455800</v>
+        <v>1327100</v>
       </c>
       <c r="I45" s="3">
-        <v>2536200</v>
+        <v>1378000</v>
       </c>
       <c r="J45" s="3">
+        <v>2400800</v>
+      </c>
+      <c r="K45" s="3">
         <v>2437300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2133500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2160500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2308900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2275900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2209100</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>14990300</v>
+        <v>15529700</v>
       </c>
       <c r="E46" s="3">
-        <v>16589500</v>
+        <v>14189700</v>
       </c>
       <c r="F46" s="3">
-        <v>16485200</v>
+        <v>15703400</v>
       </c>
       <c r="G46" s="3">
-        <v>15310400</v>
+        <v>15604700</v>
       </c>
       <c r="H46" s="3">
-        <v>14530900</v>
+        <v>14492700</v>
       </c>
       <c r="I46" s="3">
-        <v>15465500</v>
+        <v>13754700</v>
       </c>
       <c r="J46" s="3">
+        <v>14639500</v>
+      </c>
+      <c r="K46" s="3">
         <v>14651200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>13397400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>12904200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13650100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13988700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13883200</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2746500</v>
+        <v>2782800</v>
       </c>
       <c r="E47" s="3">
-        <v>2735600</v>
+        <v>2599800</v>
       </c>
       <c r="F47" s="3">
-        <v>2778000</v>
+        <v>2589500</v>
       </c>
       <c r="G47" s="3">
-        <v>2486500</v>
+        <v>2629600</v>
       </c>
       <c r="H47" s="3">
-        <v>2384500</v>
+        <v>2353700</v>
       </c>
       <c r="I47" s="3">
-        <v>476100</v>
+        <v>2257200</v>
       </c>
       <c r="J47" s="3">
+        <v>450600</v>
+      </c>
+      <c r="K47" s="3">
         <v>477100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>481600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>515200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>556100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>509400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>497200</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>8236300</v>
+        <v>8016700</v>
       </c>
       <c r="E48" s="3">
-        <v>8258700</v>
+        <v>7796400</v>
       </c>
       <c r="F48" s="3">
-        <v>8254000</v>
+        <v>7817600</v>
       </c>
       <c r="G48" s="3">
-        <v>7896200</v>
+        <v>7813100</v>
       </c>
       <c r="H48" s="3">
-        <v>7770600</v>
+        <v>7474400</v>
       </c>
       <c r="I48" s="3">
-        <v>7862500</v>
+        <v>7355600</v>
       </c>
       <c r="J48" s="3">
+        <v>7442500</v>
+      </c>
+      <c r="K48" s="3">
         <v>7849600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7659100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7812500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8166000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8367100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8429500</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>8899100</v>
+        <v>8679700</v>
       </c>
       <c r="E49" s="3">
-        <v>8843000</v>
+        <v>8423800</v>
       </c>
       <c r="F49" s="3">
-        <v>8652600</v>
+        <v>8370700</v>
       </c>
       <c r="G49" s="3">
-        <v>8453000</v>
+        <v>8190500</v>
       </c>
       <c r="H49" s="3">
-        <v>8449400</v>
+        <v>8001500</v>
       </c>
       <c r="I49" s="3">
-        <v>8631600</v>
+        <v>7998100</v>
       </c>
       <c r="J49" s="3">
+        <v>8170600</v>
+      </c>
+      <c r="K49" s="3">
         <v>8677100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8466100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8626300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9054200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9078800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9087100</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2278,8 +2391,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2319,49 +2435,55 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1635500</v>
+        <v>1619700</v>
       </c>
       <c r="E52" s="3">
-        <v>1445300</v>
+        <v>1548200</v>
       </c>
       <c r="F52" s="3">
-        <v>1380800</v>
+        <v>1368100</v>
       </c>
       <c r="G52" s="3">
-        <v>1297800</v>
+        <v>1307100</v>
       </c>
       <c r="H52" s="3">
-        <v>1208500</v>
+        <v>1228500</v>
       </c>
       <c r="I52" s="3">
-        <v>3293400</v>
+        <v>1143900</v>
       </c>
       <c r="J52" s="3">
+        <v>3117500</v>
+      </c>
+      <c r="K52" s="3">
         <v>3084000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2829500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2780400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2837000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2948300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2900900</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2401,49 +2523,55 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>36507700</v>
+        <v>36628600</v>
       </c>
       <c r="E54" s="3">
-        <v>37872100</v>
+        <v>34557800</v>
       </c>
       <c r="F54" s="3">
-        <v>37550600</v>
+        <v>35849200</v>
       </c>
       <c r="G54" s="3">
-        <v>35443900</v>
+        <v>35545000</v>
       </c>
       <c r="H54" s="3">
-        <v>34343900</v>
+        <v>33550800</v>
       </c>
       <c r="I54" s="3">
-        <v>35729100</v>
+        <v>32509500</v>
       </c>
       <c r="J54" s="3">
+        <v>33820700</v>
+      </c>
+      <c r="K54" s="3">
         <v>34738900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32833600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32638600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34263500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34892400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34797900</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2459,8 +2587,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2476,254 +2605,273 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2088900</v>
+        <v>2323600</v>
       </c>
       <c r="E57" s="3">
-        <v>2319000</v>
+        <v>1977400</v>
       </c>
       <c r="F57" s="3">
-        <v>2429800</v>
+        <v>2195100</v>
       </c>
       <c r="G57" s="3">
-        <v>2456900</v>
+        <v>2300000</v>
       </c>
       <c r="H57" s="3">
-        <v>2399000</v>
+        <v>2325700</v>
       </c>
       <c r="I57" s="3">
-        <v>2648800</v>
+        <v>2270800</v>
       </c>
       <c r="J57" s="3">
+        <v>2507300</v>
+      </c>
+      <c r="K57" s="3">
         <v>2467100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2333300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2326200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2363400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2294200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2332900</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>2603000</v>
+        <v>2985200</v>
       </c>
       <c r="E58" s="3">
-        <v>4095000</v>
+        <v>2464000</v>
       </c>
       <c r="F58" s="3">
-        <v>3617600</v>
+        <v>3876300</v>
       </c>
       <c r="G58" s="3">
-        <v>2944000</v>
+        <v>3424400</v>
       </c>
       <c r="H58" s="3">
-        <v>1997600</v>
+        <v>2786800</v>
       </c>
       <c r="I58" s="3">
-        <v>1636400</v>
+        <v>1890900</v>
       </c>
       <c r="J58" s="3">
+        <v>1549000</v>
+      </c>
+      <c r="K58" s="3">
         <v>907400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>963500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>308400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2493700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2540900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3014200</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>5008100</v>
+        <v>4795500</v>
       </c>
       <c r="E59" s="3">
-        <v>5214600</v>
+        <v>4740600</v>
       </c>
       <c r="F59" s="3">
-        <v>5062100</v>
+        <v>4936100</v>
       </c>
       <c r="G59" s="3">
-        <v>4764900</v>
+        <v>4791700</v>
       </c>
       <c r="H59" s="3">
-        <v>4805900</v>
+        <v>4510400</v>
       </c>
       <c r="I59" s="3">
-        <v>4742700</v>
+        <v>4549200</v>
       </c>
       <c r="J59" s="3">
+        <v>4489400</v>
+      </c>
+      <c r="K59" s="3">
         <v>4570700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4265600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4653300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4839300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4883300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4769000</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>9700000</v>
+        <v>10104200</v>
       </c>
       <c r="E60" s="3">
-        <v>11628600</v>
+        <v>9181900</v>
       </c>
       <c r="F60" s="3">
-        <v>11109500</v>
+        <v>11007500</v>
       </c>
       <c r="G60" s="3">
-        <v>10165800</v>
+        <v>10516100</v>
       </c>
       <c r="H60" s="3">
-        <v>9202500</v>
+        <v>9622800</v>
       </c>
       <c r="I60" s="3">
-        <v>9027900</v>
+        <v>8711000</v>
       </c>
       <c r="J60" s="3">
+        <v>8545700</v>
+      </c>
+      <c r="K60" s="3">
         <v>7945200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7562300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7287900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9696400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9718400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10116000</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>19900</v>
+        <v>673800</v>
       </c>
       <c r="E61" s="3">
-        <v>19700</v>
+        <v>18800</v>
       </c>
       <c r="F61" s="3">
-        <v>16400</v>
+        <v>18600</v>
       </c>
       <c r="G61" s="3">
-        <v>15900</v>
+        <v>15500</v>
       </c>
       <c r="H61" s="3">
-        <v>16300</v>
+        <v>15100</v>
       </c>
       <c r="I61" s="3">
-        <v>1215300</v>
+        <v>15400</v>
       </c>
       <c r="J61" s="3">
+        <v>1150400</v>
+      </c>
+      <c r="K61" s="3">
         <v>1215500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1192900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1234900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>42700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>41700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>2485300</v>
+        <v>2377800</v>
       </c>
       <c r="E62" s="3">
-        <v>2394500</v>
+        <v>2352600</v>
       </c>
       <c r="F62" s="3">
-        <v>2531100</v>
+        <v>2266600</v>
       </c>
       <c r="G62" s="3">
-        <v>2476400</v>
+        <v>2395900</v>
       </c>
       <c r="H62" s="3">
-        <v>2552600</v>
+        <v>2344100</v>
       </c>
       <c r="I62" s="3">
-        <v>2878400</v>
+        <v>2416300</v>
       </c>
       <c r="J62" s="3">
+        <v>2724700</v>
+      </c>
+      <c r="K62" s="3">
         <v>2906500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2842100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2829600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3188900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3366400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3458200</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2763,8 +2911,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2804,8 +2955,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2845,49 +2999,55 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>13908400</v>
+        <v>14770100</v>
       </c>
       <c r="E66" s="3">
-        <v>15689400</v>
+        <v>13165500</v>
       </c>
       <c r="F66" s="3">
-        <v>15299500</v>
+        <v>14851400</v>
       </c>
       <c r="G66" s="3">
-        <v>14262900</v>
+        <v>14482300</v>
       </c>
       <c r="H66" s="3">
-        <v>13361500</v>
+        <v>13501100</v>
       </c>
       <c r="I66" s="3">
-        <v>14682600</v>
+        <v>12647900</v>
       </c>
       <c r="J66" s="3">
+        <v>13898400</v>
+      </c>
+      <c r="K66" s="3">
         <v>13620300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13099800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12895800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14507600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14713500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15171700</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2903,8 +3063,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2944,8 +3105,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2985,8 +3149,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3026,8 +3193,11 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3067,49 +3237,55 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>26035600</v>
+        <v>24586300</v>
       </c>
       <c r="E72" s="3">
-        <v>25492600</v>
+        <v>24645000</v>
       </c>
       <c r="F72" s="3">
-        <v>25545200</v>
+        <v>24130900</v>
       </c>
       <c r="G72" s="3">
-        <v>25104600</v>
+        <v>24180700</v>
       </c>
       <c r="H72" s="3">
-        <v>25135100</v>
+        <v>23763700</v>
       </c>
       <c r="I72" s="3">
-        <v>24563300</v>
+        <v>23792600</v>
       </c>
       <c r="J72" s="3">
+        <v>23251300</v>
+      </c>
+      <c r="K72" s="3">
         <v>24615100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23858000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>24773600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>25558200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26037900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>25588500</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3149,8 +3325,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3190,8 +3369,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3231,49 +3413,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>22599400</v>
+        <v>21858500</v>
       </c>
       <c r="E76" s="3">
-        <v>22182700</v>
+        <v>21392300</v>
       </c>
       <c r="F76" s="3">
-        <v>22251100</v>
+        <v>20997900</v>
       </c>
       <c r="G76" s="3">
-        <v>21181000</v>
+        <v>21062600</v>
       </c>
       <c r="H76" s="3">
-        <v>20982300</v>
+        <v>20049700</v>
       </c>
       <c r="I76" s="3">
-        <v>21046500</v>
+        <v>19861600</v>
       </c>
       <c r="J76" s="3">
+        <v>19922400</v>
+      </c>
+      <c r="K76" s="3">
         <v>21118600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19733900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19742800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19755900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20178900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19626200</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3313,95 +3501,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>543000</v>
+        <v>382500</v>
       </c>
       <c r="E81" s="3">
-        <v>418800</v>
+        <v>514000</v>
       </c>
       <c r="F81" s="3">
-        <v>440800</v>
+        <v>396400</v>
       </c>
       <c r="G81" s="3">
-        <v>380200</v>
+        <v>417300</v>
       </c>
       <c r="H81" s="3">
-        <v>571800</v>
+        <v>359900</v>
       </c>
       <c r="I81" s="3">
-        <v>364800</v>
+        <v>541300</v>
       </c>
       <c r="J81" s="3">
+        <v>345300</v>
+      </c>
+      <c r="K81" s="3">
         <v>397800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>305300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>410800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>355600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>449400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3417,49 +3614,53 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>435200</v>
+        <v>347400</v>
       </c>
       <c r="E83" s="3">
-        <v>424100</v>
+        <v>411900</v>
       </c>
       <c r="F83" s="3">
-        <v>395800</v>
+        <v>401400</v>
       </c>
       <c r="G83" s="3">
-        <v>353700</v>
+        <v>374700</v>
       </c>
       <c r="H83" s="3">
-        <v>406200</v>
+        <v>334800</v>
       </c>
       <c r="I83" s="3">
-        <v>371500</v>
+        <v>384500</v>
       </c>
       <c r="J83" s="3">
+        <v>351700</v>
+      </c>
+      <c r="K83" s="3">
         <v>382500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>360900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>411300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>392200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>412300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>374000</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3499,8 +3700,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3540,8 +3744,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3581,8 +3788,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3622,8 +3832,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3663,49 +3876,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>1222000</v>
+        <v>492700</v>
       </c>
       <c r="E89" s="3">
-        <v>780700</v>
+        <v>1156700</v>
       </c>
       <c r="F89" s="3">
-        <v>542200</v>
+        <v>739000</v>
       </c>
       <c r="G89" s="3">
-        <v>496100</v>
+        <v>513300</v>
       </c>
       <c r="H89" s="3">
-        <v>499600</v>
+        <v>469600</v>
       </c>
       <c r="I89" s="3">
-        <v>403700</v>
+        <v>472900</v>
       </c>
       <c r="J89" s="3">
+        <v>382200</v>
+      </c>
+      <c r="K89" s="3">
         <v>762700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>102400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>694300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>557800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1053700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>950000</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3721,49 +3940,53 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-52668000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-73360000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-66263000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-47371000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-43314000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-56276000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-44602000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-40183000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-47466000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-54255000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-41155000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-299600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-302700</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3803,8 +4026,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3844,49 +4070,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-480900</v>
+        <v>-558100</v>
       </c>
       <c r="E94" s="3">
-        <v>-739100</v>
+        <v>-455200</v>
       </c>
       <c r="F94" s="3">
-        <v>-379100</v>
+        <v>-699600</v>
       </c>
       <c r="G94" s="3">
-        <v>-257000</v>
+        <v>-358800</v>
       </c>
       <c r="H94" s="3">
-        <v>-326700</v>
+        <v>-243200</v>
       </c>
       <c r="I94" s="3">
-        <v>-330000</v>
+        <v>-309200</v>
       </c>
       <c r="J94" s="3">
+        <v>-312300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-325800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-232700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-404700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-490000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-302300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-288600</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3902,49 +4134,53 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-441200</v>
       </c>
       <c r="E96" s="3">
-        <v>-471400</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-446200</v>
       </c>
       <c r="G96" s="3">
-        <v>-410700</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-388700</v>
       </c>
       <c r="I96" s="3">
-        <v>-416600</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-394300</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-381900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-339300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3984,8 +4220,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4025,8 +4264,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4066,127 +4308,139 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-1495000</v>
+        <v>676200</v>
       </c>
       <c r="E100" s="3">
-        <v>-226400</v>
+        <v>-1415100</v>
       </c>
       <c r="F100" s="3">
-        <v>154600</v>
+        <v>-214300</v>
       </c>
       <c r="G100" s="3">
-        <v>510400</v>
+        <v>146400</v>
       </c>
       <c r="H100" s="3">
-        <v>-790300</v>
+        <v>483200</v>
       </c>
       <c r="I100" s="3">
-        <v>-47700</v>
+        <v>-748100</v>
       </c>
       <c r="J100" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-409400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>253800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-875100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-362500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-469900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-189500</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-51000</v>
+        <v>79500</v>
       </c>
       <c r="E101" s="3">
-        <v>40100</v>
+        <v>-48300</v>
       </c>
       <c r="F101" s="3">
-        <v>117000</v>
+        <v>38000</v>
       </c>
       <c r="G101" s="3">
-        <v>29500</v>
+        <v>110800</v>
       </c>
       <c r="H101" s="3">
-        <v>-78100</v>
+        <v>28000</v>
       </c>
       <c r="I101" s="3">
-        <v>47900</v>
+        <v>-73900</v>
       </c>
       <c r="J101" s="3">
+        <v>45300</v>
+      </c>
+      <c r="K101" s="3">
         <v>120600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>82100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>30100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>13700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>84700</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-804900</v>
+        <v>690200</v>
       </c>
       <c r="E102" s="3">
-        <v>-144700</v>
+        <v>-761900</v>
       </c>
       <c r="F102" s="3">
-        <v>434800</v>
+        <v>-136900</v>
       </c>
       <c r="G102" s="3">
-        <v>779100</v>
+        <v>411600</v>
       </c>
       <c r="H102" s="3">
-        <v>-695500</v>
+        <v>737500</v>
       </c>
       <c r="I102" s="3">
-        <v>74000</v>
+        <v>-658400</v>
       </c>
       <c r="J102" s="3">
+        <v>70000</v>
+      </c>
+      <c r="K102" s="3">
         <v>148000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>205600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-555400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-298000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>295200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>556500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
@@ -653,205 +653,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6306800</v>
+        <v>8291300</v>
       </c>
       <c r="E8" s="3">
-        <v>7424500</v>
+        <v>7018500</v>
       </c>
       <c r="F8" s="3">
-        <v>6541100</v>
+        <v>8262400</v>
       </c>
       <c r="G8" s="3">
-        <v>6513200</v>
+        <v>7279300</v>
       </c>
       <c r="H8" s="3">
-        <v>6195800</v>
+        <v>7248300</v>
       </c>
       <c r="I8" s="3">
-        <v>7382800</v>
+        <v>6895000</v>
       </c>
       <c r="J8" s="3">
+        <v>8215900</v>
+      </c>
+      <c r="K8" s="3">
         <v>6355100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6731900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5838900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6563900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6008300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6482200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6193500</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>3254300</v>
+        <v>4375000</v>
       </c>
       <c r="E9" s="3">
-        <v>3927800</v>
+        <v>3621500</v>
       </c>
       <c r="F9" s="3">
-        <v>3465600</v>
+        <v>4371000</v>
       </c>
       <c r="G9" s="3">
-        <v>3420400</v>
+        <v>3856700</v>
       </c>
       <c r="H9" s="3">
-        <v>3299200</v>
+        <v>3806400</v>
       </c>
       <c r="I9" s="3">
-        <v>4075800</v>
+        <v>3671500</v>
       </c>
       <c r="J9" s="3">
+        <v>4535700</v>
+      </c>
+      <c r="K9" s="3">
         <v>3477500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3604300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3220100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3555900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3211100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3412700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3368400</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3052500</v>
+        <v>3916300</v>
       </c>
       <c r="E10" s="3">
-        <v>3496700</v>
+        <v>3396900</v>
       </c>
       <c r="F10" s="3">
-        <v>3075500</v>
+        <v>3891400</v>
       </c>
       <c r="G10" s="3">
-        <v>3092800</v>
+        <v>3422600</v>
       </c>
       <c r="H10" s="3">
-        <v>2896600</v>
+        <v>3441900</v>
       </c>
       <c r="I10" s="3">
-        <v>3307000</v>
+        <v>3223500</v>
       </c>
       <c r="J10" s="3">
+        <v>3680200</v>
+      </c>
+      <c r="K10" s="3">
         <v>2877600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>3127600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2618800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3008000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2797200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3069500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -868,52 +880,56 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>506900</v>
+        <v>603900</v>
       </c>
       <c r="E12" s="3">
-        <v>542800</v>
+        <v>564100</v>
       </c>
       <c r="F12" s="3">
-        <v>538000</v>
+        <v>604100</v>
       </c>
       <c r="G12" s="3">
-        <v>548700</v>
+        <v>598700</v>
       </c>
       <c r="H12" s="3">
-        <v>488100</v>
+        <v>610600</v>
       </c>
       <c r="I12" s="3">
-        <v>546500</v>
+        <v>543100</v>
       </c>
       <c r="J12" s="3">
+        <v>608200</v>
+      </c>
+      <c r="K12" s="3">
         <v>478600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>503600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>473700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>524400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>524200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>521500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +972,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1000,8 +1019,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1044,8 +1066,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1059,96 +1084,103 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5795800</v>
+        <v>7450700</v>
       </c>
       <c r="E17" s="3">
-        <v>6684500</v>
+        <v>6449900</v>
       </c>
       <c r="F17" s="3">
-        <v>6013900</v>
+        <v>7438800</v>
       </c>
       <c r="G17" s="3">
-        <v>5924500</v>
+        <v>6692600</v>
       </c>
       <c r="H17" s="3">
-        <v>5656800</v>
+        <v>6593100</v>
       </c>
       <c r="I17" s="3">
-        <v>6761700</v>
+        <v>6295200</v>
       </c>
       <c r="J17" s="3">
+        <v>7524800</v>
+      </c>
+      <c r="K17" s="3">
         <v>5835500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6068200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5333300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6046200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5584800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5914300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5674800</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>510900</v>
+        <v>840600</v>
       </c>
       <c r="E18" s="3">
-        <v>740000</v>
+        <v>568600</v>
       </c>
       <c r="F18" s="3">
-        <v>527100</v>
+        <v>823600</v>
       </c>
       <c r="G18" s="3">
-        <v>588700</v>
+        <v>586600</v>
       </c>
       <c r="H18" s="3">
-        <v>539000</v>
+        <v>655100</v>
       </c>
       <c r="I18" s="3">
-        <v>621100</v>
+        <v>599800</v>
       </c>
       <c r="J18" s="3">
+        <v>691100</v>
+      </c>
+      <c r="K18" s="3">
         <v>519600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>663700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>505600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>517700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>423400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>567900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>518600</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1165,228 +1197,244 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>62300</v>
+        <v>104200</v>
       </c>
       <c r="E20" s="3">
-        <v>-2600</v>
+        <v>69400</v>
       </c>
       <c r="F20" s="3">
-        <v>34200</v>
+        <v>-2900</v>
       </c>
       <c r="G20" s="3">
-        <v>59600</v>
+        <v>38000</v>
       </c>
       <c r="H20" s="3">
-        <v>21600</v>
+        <v>66300</v>
       </c>
       <c r="I20" s="3">
-        <v>149500</v>
+        <v>24100</v>
       </c>
       <c r="J20" s="3">
+        <v>166400</v>
+      </c>
+      <c r="K20" s="3">
         <v>-13800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-87500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-54500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-24700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>149200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>63800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>920600</v>
+        <v>1363000</v>
       </c>
       <c r="E21" s="3">
-        <v>1149300</v>
+        <v>1024500</v>
       </c>
       <c r="F21" s="3">
-        <v>962700</v>
+        <v>1279000</v>
       </c>
       <c r="G21" s="3">
-        <v>1023000</v>
+        <v>1071400</v>
       </c>
       <c r="H21" s="3">
-        <v>895300</v>
+        <v>1138400</v>
       </c>
       <c r="I21" s="3">
-        <v>1155100</v>
+        <v>996400</v>
       </c>
       <c r="J21" s="3">
+        <v>1285400</v>
+      </c>
+      <c r="K21" s="3">
         <v>857500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>958700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>811900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>904400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>964800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1044000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>860700</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="E22" s="3">
-        <v>5100</v>
+        <v>4500</v>
       </c>
       <c r="F22" s="3">
-        <v>4200</v>
+        <v>5600</v>
       </c>
       <c r="G22" s="3">
-        <v>3100</v>
+        <v>4700</v>
       </c>
       <c r="H22" s="3">
-        <v>2100</v>
+        <v>3400</v>
       </c>
       <c r="I22" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1300</v>
+      </c>
+      <c r="L22" s="3">
         <v>2000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="M22" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="O22" s="3">
+        <v>700</v>
+      </c>
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="K22" s="3">
-        <v>2000</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1600</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>700</v>
-      </c>
-      <c r="O22" s="3">
-        <v>1300</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>569200</v>
+        <v>938800</v>
       </c>
       <c r="E23" s="3">
-        <v>732300</v>
+        <v>633500</v>
       </c>
       <c r="F23" s="3">
-        <v>557100</v>
+        <v>815000</v>
       </c>
       <c r="G23" s="3">
-        <v>645200</v>
+        <v>620000</v>
       </c>
       <c r="H23" s="3">
-        <v>558500</v>
+        <v>718000</v>
       </c>
       <c r="I23" s="3">
-        <v>768600</v>
+        <v>621500</v>
       </c>
       <c r="J23" s="3">
+        <v>855300</v>
+      </c>
+      <c r="K23" s="3">
         <v>504500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>574200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>449500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>491600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>571900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>630400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>159600</v>
+        <v>260900</v>
       </c>
       <c r="E24" s="3">
-        <v>181200</v>
+        <v>177600</v>
       </c>
       <c r="F24" s="3">
-        <v>136400</v>
+        <v>201600</v>
       </c>
       <c r="G24" s="3">
-        <v>196300</v>
+        <v>151800</v>
       </c>
       <c r="H24" s="3">
-        <v>164600</v>
+        <v>218500</v>
       </c>
       <c r="I24" s="3">
-        <v>193900</v>
+        <v>183200</v>
       </c>
       <c r="J24" s="3">
+        <v>215800</v>
+      </c>
+      <c r="K24" s="3">
         <v>139300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>149800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>118900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>55900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>180300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>156200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>128500</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1429,96 +1477,105 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>409600</v>
+        <v>677900</v>
       </c>
       <c r="E26" s="3">
-        <v>551200</v>
+        <v>455900</v>
       </c>
       <c r="F26" s="3">
-        <v>420700</v>
+        <v>613400</v>
       </c>
       <c r="G26" s="3">
-        <v>448900</v>
+        <v>468200</v>
       </c>
       <c r="H26" s="3">
-        <v>393800</v>
+        <v>499600</v>
       </c>
       <c r="I26" s="3">
-        <v>574700</v>
+        <v>438300</v>
       </c>
       <c r="J26" s="3">
+        <v>639500</v>
+      </c>
+      <c r="K26" s="3">
         <v>365200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>424400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>330600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>435700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>391700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>474200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>382500</v>
+        <v>638000</v>
       </c>
       <c r="E27" s="3">
-        <v>514000</v>
+        <v>425600</v>
       </c>
       <c r="F27" s="3">
-        <v>396400</v>
+        <v>572000</v>
       </c>
       <c r="G27" s="3">
-        <v>417300</v>
+        <v>441200</v>
       </c>
       <c r="H27" s="3">
-        <v>359900</v>
+        <v>464400</v>
       </c>
       <c r="I27" s="3">
-        <v>541300</v>
+        <v>400500</v>
       </c>
       <c r="J27" s="3">
+        <v>602400</v>
+      </c>
+      <c r="K27" s="3">
         <v>345300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>397800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>305300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>410800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>355600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>449400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1561,8 +1618,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1605,8 +1665,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1649,8 +1712,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1693,96 +1759,105 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-62300</v>
+        <v>-104200</v>
       </c>
       <c r="E32" s="3">
-        <v>2600</v>
+        <v>-69400</v>
       </c>
       <c r="F32" s="3">
-        <v>-34200</v>
+        <v>2900</v>
       </c>
       <c r="G32" s="3">
-        <v>-59600</v>
+        <v>-38000</v>
       </c>
       <c r="H32" s="3">
-        <v>-21600</v>
+        <v>-66300</v>
       </c>
       <c r="I32" s="3">
-        <v>-149500</v>
+        <v>-24100</v>
       </c>
       <c r="J32" s="3">
+        <v>-166400</v>
+      </c>
+      <c r="K32" s="3">
         <v>13800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>87500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>54500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>24700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-149200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-63800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>382500</v>
+        <v>638000</v>
       </c>
       <c r="E33" s="3">
-        <v>514000</v>
+        <v>425600</v>
       </c>
       <c r="F33" s="3">
-        <v>396400</v>
+        <v>572000</v>
       </c>
       <c r="G33" s="3">
-        <v>417300</v>
+        <v>441200</v>
       </c>
       <c r="H33" s="3">
-        <v>359900</v>
+        <v>464400</v>
       </c>
       <c r="I33" s="3">
-        <v>541300</v>
+        <v>400500</v>
       </c>
       <c r="J33" s="3">
+        <v>602400</v>
+      </c>
+      <c r="K33" s="3">
         <v>345300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>397800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>305300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>410800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>355600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>449400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1825,101 +1900,110 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>382500</v>
+        <v>638000</v>
       </c>
       <c r="E35" s="3">
-        <v>514000</v>
+        <v>425600</v>
       </c>
       <c r="F35" s="3">
-        <v>396400</v>
+        <v>572000</v>
       </c>
       <c r="G35" s="3">
-        <v>417300</v>
+        <v>441200</v>
       </c>
       <c r="H35" s="3">
-        <v>359900</v>
+        <v>464400</v>
       </c>
       <c r="I35" s="3">
-        <v>541300</v>
+        <v>400500</v>
       </c>
       <c r="J35" s="3">
+        <v>602400</v>
+      </c>
+      <c r="K35" s="3">
         <v>345300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>397800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>305300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>410800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>355600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>449400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1936,8 +2020,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1954,87 +2039,91 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>3250700</v>
+        <v>4214100</v>
       </c>
       <c r="E41" s="3">
-        <v>2560400</v>
+        <v>3617500</v>
       </c>
       <c r="F41" s="3">
-        <v>3322400</v>
+        <v>2849400</v>
       </c>
       <c r="G41" s="3">
-        <v>3459300</v>
+        <v>3697300</v>
       </c>
       <c r="H41" s="3">
-        <v>3047700</v>
+        <v>3849700</v>
       </c>
       <c r="I41" s="3">
-        <v>2310200</v>
+        <v>3391700</v>
       </c>
       <c r="J41" s="3">
+        <v>2570900</v>
+      </c>
+      <c r="K41" s="3">
         <v>2968600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3062100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2870900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2757600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3477000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3848200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3553000</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>25100</v>
+        <v>29400</v>
       </c>
       <c r="E42" s="3">
-        <v>24400</v>
+        <v>27900</v>
       </c>
       <c r="F42" s="3">
-        <v>27600</v>
+        <v>27100</v>
       </c>
       <c r="G42" s="3">
-        <v>19600</v>
+        <v>30700</v>
       </c>
       <c r="H42" s="3">
-        <v>50200</v>
+        <v>21800</v>
       </c>
       <c r="I42" s="3">
-        <v>69600</v>
+        <v>55900</v>
       </c>
       <c r="J42" s="3">
+        <v>77400</v>
+      </c>
+      <c r="K42" s="3">
         <v>77900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>57600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>23200</v>
-      </c>
-      <c r="N42" s="3">
-        <v>700</v>
       </c>
       <c r="O42" s="3">
         <v>700</v>
@@ -2042,316 +2131,340 @@
       <c r="P42" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>4979900</v>
+        <v>5967100</v>
       </c>
       <c r="E43" s="3">
-        <v>5043100</v>
+        <v>5541900</v>
       </c>
       <c r="F43" s="3">
-        <v>4887000</v>
+        <v>5612200</v>
       </c>
       <c r="G43" s="3">
-        <v>4790000</v>
+        <v>5438500</v>
       </c>
       <c r="H43" s="3">
-        <v>4588300</v>
+        <v>5330600</v>
       </c>
       <c r="I43" s="3">
-        <v>4839900</v>
+        <v>5106100</v>
       </c>
       <c r="J43" s="3">
+        <v>5386100</v>
+      </c>
+      <c r="K43" s="3">
         <v>3552900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3714700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3497900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3493500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3275800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3533700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3740600</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>5709300</v>
+        <v>6478600</v>
       </c>
       <c r="E44" s="3">
-        <v>5084100</v>
+        <v>6353600</v>
       </c>
       <c r="F44" s="3">
-        <v>5830500</v>
+        <v>5657900</v>
       </c>
       <c r="G44" s="3">
-        <v>5730000</v>
+        <v>6488500</v>
       </c>
       <c r="H44" s="3">
-        <v>5479300</v>
+        <v>6376700</v>
       </c>
       <c r="I44" s="3">
-        <v>5157000</v>
+        <v>6097700</v>
       </c>
       <c r="J44" s="3">
+        <v>5739000</v>
+      </c>
+      <c r="K44" s="3">
         <v>5639300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5379400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4868500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4469400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4587800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4330100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4379900</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>1564800</v>
+        <v>1851000</v>
       </c>
       <c r="E45" s="3">
-        <v>1477600</v>
+        <v>1741400</v>
       </c>
       <c r="F45" s="3">
-        <v>1636000</v>
+        <v>1644400</v>
       </c>
       <c r="G45" s="3">
-        <v>1605800</v>
+        <v>1820600</v>
       </c>
       <c r="H45" s="3">
-        <v>1327100</v>
+        <v>1787000</v>
       </c>
       <c r="I45" s="3">
-        <v>1378000</v>
+        <v>1476800</v>
       </c>
       <c r="J45" s="3">
+        <v>1533500</v>
+      </c>
+      <c r="K45" s="3">
         <v>2400800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2437300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2133500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2160500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2308900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2275900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2209100</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>15529700</v>
+        <v>18540200</v>
       </c>
       <c r="E46" s="3">
-        <v>14189700</v>
+        <v>17282300</v>
       </c>
       <c r="F46" s="3">
-        <v>15703400</v>
+        <v>15791000</v>
       </c>
       <c r="G46" s="3">
-        <v>15604700</v>
+        <v>17475600</v>
       </c>
       <c r="H46" s="3">
-        <v>14492700</v>
+        <v>17365700</v>
       </c>
       <c r="I46" s="3">
-        <v>13754700</v>
+        <v>16128200</v>
       </c>
       <c r="J46" s="3">
+        <v>15307000</v>
+      </c>
+      <c r="K46" s="3">
         <v>14639500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14651200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13397400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>12904200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13650100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13988700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13883200</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2782800</v>
+        <v>3381200</v>
       </c>
       <c r="E47" s="3">
-        <v>2599800</v>
+        <v>3096800</v>
       </c>
       <c r="F47" s="3">
-        <v>2589500</v>
+        <v>2893200</v>
       </c>
       <c r="G47" s="3">
-        <v>2629600</v>
+        <v>2881700</v>
       </c>
       <c r="H47" s="3">
-        <v>2353700</v>
+        <v>2926400</v>
       </c>
       <c r="I47" s="3">
-        <v>2257200</v>
+        <v>2619300</v>
       </c>
       <c r="J47" s="3">
+        <v>2511900</v>
+      </c>
+      <c r="K47" s="3">
         <v>450600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>477100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>481600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>515200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>556100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>509400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>497200</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>8016700</v>
+        <v>9158600</v>
       </c>
       <c r="E48" s="3">
-        <v>7796400</v>
+        <v>8921400</v>
       </c>
       <c r="F48" s="3">
-        <v>7817600</v>
+        <v>8676200</v>
       </c>
       <c r="G48" s="3">
-        <v>7813100</v>
+        <v>8699800</v>
       </c>
       <c r="H48" s="3">
-        <v>7474400</v>
+        <v>8694800</v>
       </c>
       <c r="I48" s="3">
-        <v>7355600</v>
+        <v>8317900</v>
       </c>
       <c r="J48" s="3">
+        <v>8185600</v>
+      </c>
+      <c r="K48" s="3">
         <v>7442500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7849600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7659100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7812500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8166000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8367100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8429500</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>8679700</v>
+        <v>9928300</v>
       </c>
       <c r="E49" s="3">
-        <v>8423800</v>
+        <v>9659200</v>
       </c>
       <c r="F49" s="3">
-        <v>8370700</v>
+        <v>9374400</v>
       </c>
       <c r="G49" s="3">
-        <v>8190500</v>
+        <v>9315300</v>
       </c>
       <c r="H49" s="3">
-        <v>8001500</v>
+        <v>9114800</v>
       </c>
       <c r="I49" s="3">
-        <v>7998100</v>
+        <v>8904500</v>
       </c>
       <c r="J49" s="3">
+        <v>8900700</v>
+      </c>
+      <c r="K49" s="3">
         <v>8170600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8677100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8466100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8626300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9054200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9078800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9087100</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2394,8 +2507,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,52 +2554,58 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1619700</v>
+        <v>1900100</v>
       </c>
       <c r="E52" s="3">
-        <v>1548200</v>
+        <v>1802500</v>
       </c>
       <c r="F52" s="3">
-        <v>1368100</v>
+        <v>1722900</v>
       </c>
       <c r="G52" s="3">
-        <v>1307100</v>
+        <v>1522500</v>
       </c>
       <c r="H52" s="3">
-        <v>1228500</v>
+        <v>1454600</v>
       </c>
       <c r="I52" s="3">
-        <v>1143900</v>
+        <v>1367100</v>
       </c>
       <c r="J52" s="3">
+        <v>1273000</v>
+      </c>
+      <c r="K52" s="3">
         <v>3117500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3084000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2829500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2780400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2837000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2948300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2900900</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2526,52 +2648,58 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>36628600</v>
+        <v>42908500</v>
       </c>
       <c r="E54" s="3">
-        <v>34557800</v>
+        <v>40762200</v>
       </c>
       <c r="F54" s="3">
-        <v>35849200</v>
+        <v>38457700</v>
       </c>
       <c r="G54" s="3">
-        <v>35545000</v>
+        <v>39894900</v>
       </c>
       <c r="H54" s="3">
-        <v>33550800</v>
+        <v>39556300</v>
       </c>
       <c r="I54" s="3">
-        <v>32509500</v>
+        <v>37337100</v>
       </c>
       <c r="J54" s="3">
+        <v>36178300</v>
+      </c>
+      <c r="K54" s="3">
         <v>33820700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>34738900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32833600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32638600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34263500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34892400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34797900</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2588,8 +2716,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2606,272 +2735,291 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2323600</v>
+        <v>2662700</v>
       </c>
       <c r="E57" s="3">
-        <v>1977400</v>
+        <v>2585800</v>
       </c>
       <c r="F57" s="3">
-        <v>2195100</v>
+        <v>2200500</v>
       </c>
       <c r="G57" s="3">
-        <v>2300000</v>
+        <v>2442900</v>
       </c>
       <c r="H57" s="3">
-        <v>2325700</v>
+        <v>2559500</v>
       </c>
       <c r="I57" s="3">
-        <v>2270800</v>
+        <v>2588200</v>
       </c>
       <c r="J57" s="3">
+        <v>2527100</v>
+      </c>
+      <c r="K57" s="3">
         <v>2507300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2467100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2333300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2326200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2363400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2294200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2332900</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>2985200</v>
+        <v>3769800</v>
       </c>
       <c r="E58" s="3">
-        <v>2464000</v>
+        <v>3322000</v>
       </c>
       <c r="F58" s="3">
-        <v>3876300</v>
+        <v>2742000</v>
       </c>
       <c r="G58" s="3">
-        <v>3424400</v>
+        <v>4313800</v>
       </c>
       <c r="H58" s="3">
-        <v>2786800</v>
+        <v>3810800</v>
       </c>
       <c r="I58" s="3">
-        <v>1890900</v>
+        <v>3101200</v>
       </c>
       <c r="J58" s="3">
+        <v>2104300</v>
+      </c>
+      <c r="K58" s="3">
         <v>1549000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>907400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>963500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>308400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2493700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2540900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3014200</v>
       </c>
     </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>4795500</v>
+        <v>5923700</v>
       </c>
       <c r="E59" s="3">
-        <v>4740600</v>
+        <v>5336600</v>
       </c>
       <c r="F59" s="3">
-        <v>4936100</v>
+        <v>5275600</v>
       </c>
       <c r="G59" s="3">
-        <v>4791700</v>
+        <v>5493100</v>
       </c>
       <c r="H59" s="3">
-        <v>4510400</v>
+        <v>5332500</v>
       </c>
       <c r="I59" s="3">
-        <v>4549200</v>
+        <v>5019400</v>
       </c>
       <c r="J59" s="3">
+        <v>5062600</v>
+      </c>
+      <c r="K59" s="3">
         <v>4489400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4570700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4265600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4653300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4839300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4883300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4769000</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>10104200</v>
+        <v>12356100</v>
       </c>
       <c r="E60" s="3">
-        <v>9181900</v>
+        <v>11244500</v>
       </c>
       <c r="F60" s="3">
-        <v>11007500</v>
+        <v>10218100</v>
       </c>
       <c r="G60" s="3">
-        <v>10516100</v>
+        <v>12249700</v>
       </c>
       <c r="H60" s="3">
-        <v>9622800</v>
+        <v>11702800</v>
       </c>
       <c r="I60" s="3">
-        <v>8711000</v>
+        <v>10708800</v>
       </c>
       <c r="J60" s="3">
+        <v>9694000</v>
+      </c>
+      <c r="K60" s="3">
         <v>8545700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7945200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7562300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7287900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9696400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9718400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10116000</v>
       </c>
     </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>673800</v>
+        <v>749300</v>
       </c>
       <c r="E61" s="3">
-        <v>18800</v>
+        <v>749800</v>
       </c>
       <c r="F61" s="3">
-        <v>18600</v>
+        <v>21000</v>
       </c>
       <c r="G61" s="3">
-        <v>15500</v>
+        <v>20700</v>
       </c>
       <c r="H61" s="3">
-        <v>15100</v>
+        <v>17300</v>
       </c>
       <c r="I61" s="3">
-        <v>15400</v>
+        <v>16700</v>
       </c>
       <c r="J61" s="3">
+        <v>17200</v>
+      </c>
+      <c r="K61" s="3">
         <v>1150400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1215500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1192900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1234900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>42700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>41700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>2377800</v>
+        <v>2774400</v>
       </c>
       <c r="E62" s="3">
-        <v>2352600</v>
+        <v>2646100</v>
       </c>
       <c r="F62" s="3">
-        <v>2266600</v>
+        <v>2618100</v>
       </c>
       <c r="G62" s="3">
-        <v>2395900</v>
+        <v>2522400</v>
       </c>
       <c r="H62" s="3">
-        <v>2344100</v>
+        <v>2666300</v>
       </c>
       <c r="I62" s="3">
-        <v>2416300</v>
+        <v>2608700</v>
       </c>
       <c r="J62" s="3">
+        <v>2689000</v>
+      </c>
+      <c r="K62" s="3">
         <v>2724700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2906500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2842100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2829600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3188900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3366400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3458200</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2914,8 +3062,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2958,8 +3109,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3002,52 +3156,58 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>14770100</v>
+        <v>17726900</v>
       </c>
       <c r="E66" s="3">
-        <v>13165500</v>
+        <v>16436900</v>
       </c>
       <c r="F66" s="3">
-        <v>14851400</v>
+        <v>14651200</v>
       </c>
       <c r="G66" s="3">
-        <v>14482300</v>
+        <v>16527400</v>
       </c>
       <c r="H66" s="3">
-        <v>13501100</v>
+        <v>16116700</v>
       </c>
       <c r="I66" s="3">
-        <v>12647900</v>
+        <v>15024700</v>
       </c>
       <c r="J66" s="3">
+        <v>14075200</v>
+      </c>
+      <c r="K66" s="3">
         <v>13898400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13620300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13099800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12895800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14507600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14713500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15171700</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3064,8 +3224,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3108,8 +3269,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3152,8 +3316,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3196,8 +3363,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3240,52 +3410,58 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>24586300</v>
+        <v>27993400</v>
       </c>
       <c r="E72" s="3">
-        <v>24645000</v>
+        <v>27360900</v>
       </c>
       <c r="F72" s="3">
-        <v>24130900</v>
+        <v>27426200</v>
       </c>
       <c r="G72" s="3">
-        <v>24180700</v>
+        <v>26854200</v>
       </c>
       <c r="H72" s="3">
-        <v>23763700</v>
+        <v>26909600</v>
       </c>
       <c r="I72" s="3">
-        <v>23792600</v>
+        <v>26445500</v>
       </c>
       <c r="J72" s="3">
+        <v>26477600</v>
+      </c>
+      <c r="K72" s="3">
         <v>23251300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>24615100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23858000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>24773600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>25558200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>26037900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>25588500</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3328,8 +3504,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3372,8 +3551,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3416,52 +3598,58 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>21858500</v>
+        <v>25181600</v>
       </c>
       <c r="E76" s="3">
-        <v>21392300</v>
+        <v>24325300</v>
       </c>
       <c r="F76" s="3">
-        <v>20997900</v>
+        <v>23806500</v>
       </c>
       <c r="G76" s="3">
-        <v>21062600</v>
+        <v>23367600</v>
       </c>
       <c r="H76" s="3">
-        <v>20049700</v>
+        <v>23439600</v>
       </c>
       <c r="I76" s="3">
-        <v>19861600</v>
+        <v>22312300</v>
       </c>
       <c r="J76" s="3">
+        <v>22103000</v>
+      </c>
+      <c r="K76" s="3">
         <v>19922400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21118600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19733900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19742800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19755900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20178900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19626200</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3504,101 +3692,110 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>382500</v>
+        <v>638000</v>
       </c>
       <c r="E81" s="3">
-        <v>514000</v>
+        <v>425600</v>
       </c>
       <c r="F81" s="3">
-        <v>396400</v>
+        <v>572000</v>
       </c>
       <c r="G81" s="3">
-        <v>417300</v>
+        <v>441200</v>
       </c>
       <c r="H81" s="3">
-        <v>359900</v>
+        <v>464400</v>
       </c>
       <c r="I81" s="3">
-        <v>541300</v>
+        <v>400500</v>
       </c>
       <c r="J81" s="3">
+        <v>602400</v>
+      </c>
+      <c r="K81" s="3">
         <v>345300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>397800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>305300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>410800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>355600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>449400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3615,52 +3812,56 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>347400</v>
+        <v>418100</v>
       </c>
       <c r="E83" s="3">
-        <v>411900</v>
+        <v>386600</v>
       </c>
       <c r="F83" s="3">
-        <v>401400</v>
+        <v>458400</v>
       </c>
       <c r="G83" s="3">
-        <v>374700</v>
+        <v>446700</v>
       </c>
       <c r="H83" s="3">
-        <v>334800</v>
+        <v>416900</v>
       </c>
       <c r="I83" s="3">
-        <v>384500</v>
+        <v>372600</v>
       </c>
       <c r="J83" s="3">
+        <v>427900</v>
+      </c>
+      <c r="K83" s="3">
         <v>351700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>382500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>360900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>411300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>392200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>412300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>374000</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3703,8 +3904,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3747,8 +3951,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3791,8 +3998,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3835,8 +4045,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3879,52 +4092,58 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>492700</v>
+        <v>1169800</v>
       </c>
       <c r="E89" s="3">
-        <v>1156700</v>
+        <v>548300</v>
       </c>
       <c r="F89" s="3">
-        <v>739000</v>
+        <v>1287300</v>
       </c>
       <c r="G89" s="3">
-        <v>513300</v>
+        <v>822400</v>
       </c>
       <c r="H89" s="3">
-        <v>469600</v>
+        <v>571200</v>
       </c>
       <c r="I89" s="3">
-        <v>472900</v>
+        <v>522600</v>
       </c>
       <c r="J89" s="3">
+        <v>526300</v>
+      </c>
+      <c r="K89" s="3">
         <v>382200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>762700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>102400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>694300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>557800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1053700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>950000</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3941,52 +4160,56 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-62100000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-52668000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-73360000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-66263000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-47371000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43314000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-56276000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-44602000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-40183000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-47466000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-54255000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41155000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-299600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-302700</v>
       </c>
     </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4029,8 +4252,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4073,52 +4299,58 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-558100</v>
+        <v>-436500</v>
       </c>
       <c r="E94" s="3">
-        <v>-455200</v>
+        <v>-621000</v>
       </c>
       <c r="F94" s="3">
-        <v>-699600</v>
+        <v>-506600</v>
       </c>
       <c r="G94" s="3">
-        <v>-358800</v>
+        <v>-778500</v>
       </c>
       <c r="H94" s="3">
-        <v>-243200</v>
+        <v>-399300</v>
       </c>
       <c r="I94" s="3">
-        <v>-309200</v>
+        <v>-270700</v>
       </c>
       <c r="J94" s="3">
+        <v>-344100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-312300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-325800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-232700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-404700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-490000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-302300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-288600</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4135,52 +4367,56 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-441200</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-490900</v>
       </c>
       <c r="F96" s="3">
-        <v>-446200</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-496600</v>
       </c>
       <c r="H96" s="3">
-        <v>-388700</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-432600</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-394300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-381900</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-339300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4223,8 +4459,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4267,8 +4506,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4311,136 +4553,148 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>676200</v>
+        <v>-271100</v>
       </c>
       <c r="E100" s="3">
-        <v>-1415100</v>
+        <v>752500</v>
       </c>
       <c r="F100" s="3">
-        <v>-214300</v>
+        <v>-1574800</v>
       </c>
       <c r="G100" s="3">
-        <v>146400</v>
+        <v>-238500</v>
       </c>
       <c r="H100" s="3">
-        <v>483200</v>
+        <v>162900</v>
       </c>
       <c r="I100" s="3">
-        <v>-748100</v>
+        <v>537700</v>
       </c>
       <c r="J100" s="3">
+        <v>-832600</v>
+      </c>
+      <c r="K100" s="3">
         <v>-45100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-409400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>253800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-875100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-362500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-469900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-189500</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>79500</v>
+        <v>134300</v>
       </c>
       <c r="E101" s="3">
-        <v>-48300</v>
+        <v>88400</v>
       </c>
       <c r="F101" s="3">
-        <v>38000</v>
+        <v>-53700</v>
       </c>
       <c r="G101" s="3">
-        <v>110800</v>
+        <v>42300</v>
       </c>
       <c r="H101" s="3">
-        <v>28000</v>
+        <v>123300</v>
       </c>
       <c r="I101" s="3">
-        <v>-73900</v>
+        <v>31100</v>
       </c>
       <c r="J101" s="3">
+        <v>-82300</v>
+      </c>
+      <c r="K101" s="3">
         <v>45300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>120600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>82100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>30100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>13700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>84700</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>690200</v>
+        <v>596600</v>
       </c>
       <c r="E102" s="3">
-        <v>-761900</v>
+        <v>768100</v>
       </c>
       <c r="F102" s="3">
-        <v>-136900</v>
+        <v>-847900</v>
       </c>
       <c r="G102" s="3">
-        <v>411600</v>
+        <v>-152400</v>
       </c>
       <c r="H102" s="3">
-        <v>737500</v>
+        <v>458000</v>
       </c>
       <c r="I102" s="3">
-        <v>-658400</v>
+        <v>820800</v>
       </c>
       <c r="J102" s="3">
+        <v>-732700</v>
+      </c>
+      <c r="K102" s="3">
         <v>70000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>148000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>205600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-555400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-298000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>295200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>556500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
   <si>
     <t>CAJPY</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -653,217 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>8291300</v>
-      </c>
-      <c r="E8" s="3">
-        <v>7018500</v>
-      </c>
-      <c r="F8" s="3">
-        <v>8262400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>7279300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>7248300</v>
-      </c>
-      <c r="I8" s="3">
-        <v>6895000</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K8" s="3">
         <v>8215900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6355100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6731900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5838900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6563900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6008300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6482200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6193500</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>4375000</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3621500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>4371000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3856700</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3806400</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3671500</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" s="3">
         <v>4535700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3477500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3604300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3220100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3555900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3211100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3412700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3368400</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>3916300</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3396900</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3891400</v>
-      </c>
-      <c r="G10" s="3">
-        <v>3422600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>3441900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>3223500</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K10" s="3">
         <v>3680200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2877600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3127600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2618800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3008000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2797200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3069500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -881,55 +902,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>603900</v>
-      </c>
-      <c r="E12" s="3">
-        <v>564100</v>
-      </c>
-      <c r="F12" s="3">
-        <v>604100</v>
-      </c>
-      <c r="G12" s="3">
-        <v>598700</v>
-      </c>
-      <c r="H12" s="3">
-        <v>610600</v>
-      </c>
-      <c r="I12" s="3">
-        <v>543100</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K12" s="3">
         <v>608200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>478600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>503600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>473700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>524400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>524200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>521500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -975,31 +1000,34 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1022,31 +1050,34 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1069,8 +1100,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1085,102 +1119,109 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
-        <v>7450700</v>
-      </c>
-      <c r="E17" s="3">
-        <v>6449900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>7438800</v>
-      </c>
-      <c r="G17" s="3">
-        <v>6692600</v>
-      </c>
-      <c r="H17" s="3">
-        <v>6593100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>6295200</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K17" s="3">
         <v>7524800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5835500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6068200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5333300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6046200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5584800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5914300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5674800</v>
       </c>
     </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
-        <v>840600</v>
-      </c>
-      <c r="E18" s="3">
-        <v>568600</v>
-      </c>
-      <c r="F18" s="3">
-        <v>823600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>586600</v>
-      </c>
-      <c r="H18" s="3">
-        <v>655100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>599800</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K18" s="3">
         <v>691100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>519600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>663700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>505600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>517700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>423400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>567900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>518600</v>
       </c>
     </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1198,243 +1239,259 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>104200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>69400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="G20" s="3">
-        <v>38000</v>
-      </c>
-      <c r="H20" s="3">
-        <v>66300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>24100</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K20" s="3">
         <v>166400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-13800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-87500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-54500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-24700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>149200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>63800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3">
-        <v>1363000</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1024500</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1279000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1071400</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1138400</v>
-      </c>
-      <c r="I21" s="3">
-        <v>996400</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K21" s="3">
         <v>1285400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>857500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>958700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>811900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>904400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>964800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1044000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>860700</v>
       </c>
     </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="3">
-        <v>6000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>4500</v>
-      </c>
-      <c r="F22" s="3">
-        <v>5600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>3400</v>
-      </c>
-      <c r="I22" s="3">
-        <v>2300</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K22" s="3">
         <v>2200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="3">
-        <v>938800</v>
-      </c>
-      <c r="E23" s="3">
-        <v>633500</v>
-      </c>
-      <c r="F23" s="3">
-        <v>815000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>620000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>718000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>621500</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K23" s="3">
         <v>855300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>504500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>574200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>449500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>491600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>571900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>630400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="3">
-        <v>260900</v>
-      </c>
-      <c r="E24" s="3">
-        <v>177600</v>
-      </c>
-      <c r="F24" s="3">
-        <v>201600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>151800</v>
-      </c>
-      <c r="H24" s="3">
-        <v>218500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>183200</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K24" s="3">
         <v>215800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>139300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>149800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>118900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>55900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>180300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>156200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>128500</v>
       </c>
     </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1480,102 +1537,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="3">
-        <v>677900</v>
-      </c>
-      <c r="E26" s="3">
-        <v>455900</v>
-      </c>
-      <c r="F26" s="3">
-        <v>613400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>468200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>499600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>438300</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K26" s="3">
         <v>639500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>365200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>424400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>330600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>435700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>391700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>474200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="3">
-        <v>638000</v>
-      </c>
-      <c r="E27" s="3">
-        <v>425600</v>
-      </c>
-      <c r="F27" s="3">
-        <v>572000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>441200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>464400</v>
-      </c>
-      <c r="I27" s="3">
-        <v>400500</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K27" s="3">
         <v>602400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>345300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>397800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>305300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>410800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>355600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>449400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1621,31 +1687,34 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1668,8 +1737,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1715,8 +1787,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1762,102 +1837,111 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D32" s="3">
-        <v>-104200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-69400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2900</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-38000</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-66300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-24100</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K32" s="3">
         <v>-166400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>13800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>87500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>54500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>24700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-149200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-63800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D33" s="3">
-        <v>638000</v>
-      </c>
-      <c r="E33" s="3">
-        <v>425600</v>
-      </c>
-      <c r="F33" s="3">
-        <v>572000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>441200</v>
-      </c>
-      <c r="H33" s="3">
-        <v>464400</v>
-      </c>
-      <c r="I33" s="3">
-        <v>400500</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K33" s="3">
         <v>602400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>345300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>397800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>305300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>410800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>355600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>449400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1903,107 +1987,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="3">
-        <v>638000</v>
-      </c>
-      <c r="E35" s="3">
-        <v>425600</v>
-      </c>
-      <c r="F35" s="3">
-        <v>572000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>441200</v>
-      </c>
-      <c r="H35" s="3">
-        <v>464400</v>
-      </c>
-      <c r="I35" s="3">
-        <v>400500</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K35" s="3">
         <v>602400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>345300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>397800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>305300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>410800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>355600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>449400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2021,8 +2114,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2040,93 +2134,97 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>4214100</v>
+        <v>3843200</v>
       </c>
       <c r="E41" s="3">
-        <v>3617500</v>
+        <v>3689700</v>
       </c>
       <c r="F41" s="3">
-        <v>2849400</v>
+        <v>3368600</v>
       </c>
       <c r="G41" s="3">
-        <v>3697300</v>
+        <v>2847000</v>
       </c>
       <c r="H41" s="3">
-        <v>3849700</v>
+        <v>3486500</v>
       </c>
       <c r="I41" s="3">
-        <v>3391700</v>
+        <v>3750100</v>
       </c>
       <c r="J41" s="3">
+        <v>3593500</v>
+      </c>
+      <c r="K41" s="3">
         <v>2570900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2968600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3062100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2870900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2757600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3477000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3848200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3553000</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>29400</v>
+        <v>34800</v>
       </c>
       <c r="E42" s="3">
-        <v>27900</v>
+        <v>25700</v>
       </c>
       <c r="F42" s="3">
+        <v>26000</v>
+      </c>
+      <c r="G42" s="3">
         <v>27100</v>
       </c>
-      <c r="G42" s="3">
-        <v>30700</v>
-      </c>
       <c r="H42" s="3">
-        <v>21800</v>
+        <v>28900</v>
       </c>
       <c r="I42" s="3">
-        <v>55900</v>
+        <v>21200</v>
       </c>
       <c r="J42" s="3">
+        <v>59200</v>
+      </c>
+      <c r="K42" s="3">
         <v>77400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>77900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>57600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>23200</v>
-      </c>
-      <c r="O42" s="3">
-        <v>700</v>
       </c>
       <c r="P42" s="3">
         <v>700</v>
@@ -2134,337 +2232,361 @@
       <c r="Q42" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>5967100</v>
+        <v>5334500</v>
       </c>
       <c r="E43" s="3">
-        <v>5541900</v>
+        <v>5224400</v>
       </c>
       <c r="F43" s="3">
-        <v>5612200</v>
+        <v>5160500</v>
       </c>
       <c r="G43" s="3">
-        <v>5438500</v>
+        <v>5929300</v>
       </c>
       <c r="H43" s="3">
-        <v>5330600</v>
+        <v>5452400</v>
       </c>
       <c r="I43" s="3">
-        <v>5106100</v>
+        <v>5548400</v>
       </c>
       <c r="J43" s="3">
+        <v>5711500</v>
+      </c>
+      <c r="K43" s="3">
         <v>5386100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3552900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3714700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3497900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3493500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3275800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3533700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3740600</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>6478600</v>
+        <v>6210100</v>
       </c>
       <c r="E44" s="3">
-        <v>6353600</v>
+        <v>5672300</v>
       </c>
       <c r="F44" s="3">
-        <v>5657900</v>
+        <v>5916300</v>
       </c>
       <c r="G44" s="3">
-        <v>6488500</v>
+        <v>5653200</v>
       </c>
       <c r="H44" s="3">
-        <v>6376700</v>
+        <v>6118500</v>
       </c>
       <c r="I44" s="3">
-        <v>6097700</v>
+        <v>6211800</v>
       </c>
       <c r="J44" s="3">
+        <v>6460600</v>
+      </c>
+      <c r="K44" s="3">
         <v>5739000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5639300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5379400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4868500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4469400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4587800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4330100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4379900</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3">
-        <v>1851000</v>
+      <c r="D45" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E45" s="3">
-        <v>1741400</v>
+        <v>1620600</v>
       </c>
       <c r="F45" s="3">
-        <v>1644400</v>
+        <v>1621500</v>
       </c>
       <c r="G45" s="3">
-        <v>1820600</v>
+        <v>27700</v>
       </c>
       <c r="H45" s="3">
-        <v>1787000</v>
+        <v>3400</v>
       </c>
       <c r="I45" s="3">
-        <v>1476800</v>
+        <v>3300</v>
       </c>
       <c r="J45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K45" s="3">
         <v>1533500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2400800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2437300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2133500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2160500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2308900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2275900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2209100</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>18540200</v>
+        <v>17114200</v>
       </c>
       <c r="E46" s="3">
-        <v>17282300</v>
+        <v>16232800</v>
       </c>
       <c r="F46" s="3">
-        <v>15791000</v>
+        <v>16092800</v>
       </c>
       <c r="G46" s="3">
-        <v>17475600</v>
+        <v>15777900</v>
       </c>
       <c r="H46" s="3">
-        <v>17365700</v>
+        <v>16479100</v>
       </c>
       <c r="I46" s="3">
-        <v>16128200</v>
+        <v>16916500</v>
       </c>
       <c r="J46" s="3">
+        <v>17088000</v>
+      </c>
+      <c r="K46" s="3">
         <v>15307000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14639500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14651200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13397400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12904200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13650100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13988700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13883200</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>3381200</v>
+        <v>556300</v>
       </c>
       <c r="E47" s="3">
-        <v>3096800</v>
+        <v>4624100</v>
       </c>
       <c r="F47" s="3">
-        <v>2893200</v>
+        <v>4562100</v>
       </c>
       <c r="G47" s="3">
-        <v>2881700</v>
+        <v>556900</v>
       </c>
       <c r="H47" s="3">
-        <v>2926400</v>
+        <v>497200</v>
       </c>
       <c r="I47" s="3">
-        <v>2619300</v>
+        <v>522600</v>
       </c>
       <c r="J47" s="3">
+        <v>515200</v>
+      </c>
+      <c r="K47" s="3">
         <v>2511900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>450600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>477100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>481600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>515200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>556100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>509400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>497200</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>9158600</v>
+        <v>8631400</v>
       </c>
       <c r="E48" s="3">
-        <v>8921400</v>
+        <v>8018800</v>
       </c>
       <c r="F48" s="3">
-        <v>8676200</v>
+        <v>8307400</v>
       </c>
       <c r="G48" s="3">
-        <v>8699800</v>
+        <v>8669000</v>
       </c>
       <c r="H48" s="3">
-        <v>8694800</v>
+        <v>8203700</v>
       </c>
       <c r="I48" s="3">
-        <v>8317900</v>
+        <v>8469900</v>
       </c>
       <c r="J48" s="3">
+        <v>8812900</v>
+      </c>
+      <c r="K48" s="3">
         <v>8185600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7442500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7849600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7659100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7812500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8166000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8367100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8429500</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>9928300</v>
+        <v>9358900</v>
       </c>
       <c r="E49" s="3">
-        <v>9659200</v>
+        <v>8692700</v>
       </c>
       <c r="F49" s="3">
-        <v>9374400</v>
+        <v>8994400</v>
       </c>
       <c r="G49" s="3">
-        <v>9315300</v>
+        <v>9366700</v>
       </c>
       <c r="H49" s="3">
-        <v>9114800</v>
+        <v>8784200</v>
       </c>
       <c r="I49" s="3">
-        <v>8904500</v>
+        <v>8879000</v>
       </c>
       <c r="J49" s="3">
+        <v>9434400</v>
+      </c>
+      <c r="K49" s="3">
         <v>8900700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8170600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8677100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8466100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8626300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9054200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9078800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9087100</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2510,8 +2632,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2557,55 +2682,61 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>1900100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1802500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1722900</v>
+        <v>2073900</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G52" s="3">
-        <v>1522500</v>
+        <v>959900</v>
       </c>
       <c r="H52" s="3">
-        <v>1454600</v>
+        <v>1518000</v>
       </c>
       <c r="I52" s="3">
-        <v>1367100</v>
+        <v>1497400</v>
       </c>
       <c r="J52" s="3">
+        <v>1536000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1273000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3117500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3084000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2829500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2780400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2837000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2948300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2900900</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2651,55 +2782,61 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>42908500</v>
+        <v>40035100</v>
       </c>
       <c r="E54" s="3">
-        <v>40762200</v>
+        <v>37568200</v>
       </c>
       <c r="F54" s="3">
-        <v>38457700</v>
+        <v>37956800</v>
       </c>
       <c r="G54" s="3">
-        <v>39894900</v>
+        <v>38425800</v>
       </c>
       <c r="H54" s="3">
-        <v>39556300</v>
+        <v>37620000</v>
       </c>
       <c r="I54" s="3">
-        <v>37337100</v>
+        <v>38533100</v>
       </c>
       <c r="J54" s="3">
+        <v>39559000</v>
+      </c>
+      <c r="K54" s="3">
         <v>36178300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33820700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34738900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32833600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32638600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34263500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34892400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34797900</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2717,8 +2854,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2736,290 +2874,309 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2662700</v>
+        <v>2474200</v>
       </c>
       <c r="E57" s="3">
-        <v>2585800</v>
+        <v>2331300</v>
       </c>
       <c r="F57" s="3">
-        <v>2200500</v>
+        <v>2407800</v>
       </c>
       <c r="G57" s="3">
-        <v>2442900</v>
+        <v>2198700</v>
       </c>
       <c r="H57" s="3">
-        <v>2559500</v>
+        <v>2303600</v>
       </c>
       <c r="I57" s="3">
-        <v>2588200</v>
+        <v>2493300</v>
       </c>
       <c r="J57" s="3">
+        <v>2742200</v>
+      </c>
+      <c r="K57" s="3">
         <v>2527100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2507300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2467100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2333300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2326200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2363400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2294200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2332900</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>3769800</v>
+        <v>4646400</v>
       </c>
       <c r="E58" s="3">
-        <v>3322000</v>
+        <v>3545700</v>
       </c>
       <c r="F58" s="3">
-        <v>2742000</v>
+        <v>3343600</v>
       </c>
       <c r="G58" s="3">
-        <v>4313800</v>
+        <v>2992000</v>
       </c>
       <c r="H58" s="3">
-        <v>3810800</v>
+        <v>4312100</v>
       </c>
       <c r="I58" s="3">
-        <v>3101200</v>
+        <v>3960400</v>
       </c>
       <c r="J58" s="3">
+        <v>3540200</v>
+      </c>
+      <c r="K58" s="3">
         <v>2104300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1549000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>907400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>963500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>308400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2493700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2540900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3014200</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>5923700</v>
+        <v>2285300</v>
       </c>
       <c r="E59" s="3">
-        <v>5336600</v>
+        <v>2449000</v>
       </c>
       <c r="F59" s="3">
-        <v>5275600</v>
+        <v>2156700</v>
       </c>
       <c r="G59" s="3">
-        <v>5493100</v>
+        <v>2534300</v>
       </c>
       <c r="H59" s="3">
-        <v>5332500</v>
+        <v>2437100</v>
       </c>
       <c r="I59" s="3">
-        <v>5019400</v>
+        <v>2682900</v>
       </c>
       <c r="J59" s="3">
+        <v>2539200</v>
+      </c>
+      <c r="K59" s="3">
         <v>5062600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4489400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4570700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4265600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4653300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4839300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4883300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4769000</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>12356100</v>
+        <v>12303200</v>
       </c>
       <c r="E60" s="3">
-        <v>11244500</v>
+        <v>10818300</v>
       </c>
       <c r="F60" s="3">
-        <v>10218100</v>
+        <v>10470600</v>
       </c>
       <c r="G60" s="3">
-        <v>12249700</v>
+        <v>10209700</v>
       </c>
       <c r="H60" s="3">
-        <v>11702800</v>
+        <v>11551200</v>
       </c>
       <c r="I60" s="3">
-        <v>10708800</v>
+        <v>11400100</v>
       </c>
       <c r="J60" s="3">
+        <v>11346100</v>
+      </c>
+      <c r="K60" s="3">
         <v>9694000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8545700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7945200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7562300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7287900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9696400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9718400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>10116000</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>749300</v>
+        <v>1393500</v>
       </c>
       <c r="E61" s="3">
-        <v>749800</v>
+        <v>1324800</v>
       </c>
       <c r="F61" s="3">
-        <v>21000</v>
+        <v>1367400</v>
       </c>
       <c r="G61" s="3">
-        <v>20700</v>
+        <v>677900</v>
       </c>
       <c r="H61" s="3">
-        <v>17300</v>
+        <v>614700</v>
       </c>
       <c r="I61" s="3">
-        <v>16700</v>
+        <v>624100</v>
       </c>
       <c r="J61" s="3">
+        <v>646100</v>
+      </c>
+      <c r="K61" s="3">
         <v>17200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1150400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1215500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1192900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1234900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>42700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>41700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>2774400</v>
+        <v>681600</v>
       </c>
       <c r="E62" s="3">
-        <v>2646100</v>
+        <v>675300</v>
       </c>
       <c r="F62" s="3">
-        <v>2618100</v>
+        <v>668400</v>
       </c>
       <c r="G62" s="3">
-        <v>2522400</v>
+        <v>450500</v>
       </c>
       <c r="H62" s="3">
-        <v>2666300</v>
+        <v>646900</v>
       </c>
       <c r="I62" s="3">
-        <v>2608700</v>
+        <v>679800</v>
       </c>
       <c r="J62" s="3">
+        <v>729600</v>
+      </c>
+      <c r="K62" s="3">
         <v>2689000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2724700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2906500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2842100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2829600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3188900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3366400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3458200</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3065,8 +3222,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3112,8 +3272,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3159,55 +3322,61 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>17726900</v>
+        <v>15541300</v>
       </c>
       <c r="E66" s="3">
-        <v>16436900</v>
+        <v>13903400</v>
       </c>
       <c r="F66" s="3">
-        <v>14651200</v>
+        <v>13632800</v>
       </c>
       <c r="G66" s="3">
-        <v>16527400</v>
+        <v>12846500</v>
       </c>
       <c r="H66" s="3">
-        <v>16116700</v>
+        <v>13949300</v>
       </c>
       <c r="I66" s="3">
-        <v>15024700</v>
+        <v>14014300</v>
       </c>
       <c r="J66" s="3">
+        <v>14127800</v>
+      </c>
+      <c r="K66" s="3">
         <v>14075200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13898400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13620300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13099800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12895800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14507600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14713500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15171700</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3225,8 +3394,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3272,8 +3442,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3319,8 +3492,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3366,8 +3542,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3413,55 +3592,61 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>27993400</v>
+        <v>27495400</v>
       </c>
       <c r="E72" s="3">
-        <v>27360900</v>
+        <v>24509400</v>
       </c>
       <c r="F72" s="3">
-        <v>27426200</v>
+        <v>25477800</v>
       </c>
       <c r="G72" s="3">
-        <v>26854200</v>
+        <v>27403500</v>
       </c>
       <c r="H72" s="3">
-        <v>26909600</v>
+        <v>25322900</v>
       </c>
       <c r="I72" s="3">
-        <v>26445500</v>
+        <v>26213500</v>
       </c>
       <c r="J72" s="3">
+        <v>28019300</v>
+      </c>
+      <c r="K72" s="3">
         <v>26477600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23251300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>24615100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23858000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>24773600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>25558200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>26037900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>25588500</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3507,8 +3692,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3554,8 +3742,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3601,55 +3792,61 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>25181600</v>
+        <v>22727100</v>
       </c>
       <c r="E76" s="3">
-        <v>24325300</v>
+        <v>22047600</v>
       </c>
       <c r="F76" s="3">
-        <v>23806500</v>
+        <v>22651100</v>
       </c>
       <c r="G76" s="3">
-        <v>23367600</v>
+        <v>23786700</v>
       </c>
       <c r="H76" s="3">
-        <v>23439600</v>
+        <v>22035100</v>
       </c>
       <c r="I76" s="3">
-        <v>22312300</v>
+        <v>22833300</v>
       </c>
       <c r="J76" s="3">
+        <v>23640100</v>
+      </c>
+      <c r="K76" s="3">
         <v>22103000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19922400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21118600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19733900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19742800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19755900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20178900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19626200</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3695,107 +3892,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D81" s="3">
-        <v>638000</v>
-      </c>
-      <c r="E81" s="3">
-        <v>425600</v>
-      </c>
-      <c r="F81" s="3">
-        <v>572000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>441200</v>
-      </c>
-      <c r="H81" s="3">
-        <v>464400</v>
-      </c>
-      <c r="I81" s="3">
-        <v>400500</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K81" s="3">
         <v>602400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>345300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>397800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>305300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>410800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>355600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>449400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3813,55 +4019,59 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>418100</v>
+        <v>421200</v>
       </c>
       <c r="E83" s="3">
-        <v>386600</v>
+        <v>406200</v>
       </c>
       <c r="F83" s="3">
-        <v>458400</v>
+        <v>394700</v>
       </c>
       <c r="G83" s="3">
-        <v>446700</v>
+        <v>457000</v>
       </c>
       <c r="H83" s="3">
-        <v>416900</v>
+        <v>381000</v>
       </c>
       <c r="I83" s="3">
-        <v>372600</v>
+        <v>417600</v>
       </c>
       <c r="J83" s="3">
+        <v>447600</v>
+      </c>
+      <c r="K83" s="3">
         <v>427900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>351700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>382500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>360900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>411300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>392200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>412300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>374000</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3907,8 +4117,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3954,8 +4167,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4001,8 +4217,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4048,8 +4267,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4095,55 +4317,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>1169800</v>
+        <v>844800</v>
       </c>
       <c r="E89" s="3">
-        <v>548300</v>
+        <v>1024200</v>
       </c>
       <c r="F89" s="3">
-        <v>1287300</v>
+        <v>510500</v>
       </c>
       <c r="G89" s="3">
-        <v>822400</v>
+        <v>1286200</v>
       </c>
       <c r="H89" s="3">
-        <v>571200</v>
+        <v>775500</v>
       </c>
       <c r="I89" s="3">
-        <v>522600</v>
+        <v>556400</v>
       </c>
       <c r="J89" s="3">
+        <v>553700</v>
+      </c>
+      <c r="K89" s="3">
         <v>526300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>382200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>762700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>102400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>694300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>557800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1053700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>950000</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4161,55 +4389,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-62100000</v>
+        <v>-406100</v>
       </c>
       <c r="E91" s="3">
-        <v>-52668000</v>
+        <v>-386000</v>
       </c>
       <c r="F91" s="3">
-        <v>-73360000</v>
+        <v>-348200</v>
       </c>
       <c r="G91" s="3">
-        <v>-66263000</v>
+        <v>-520400</v>
       </c>
       <c r="H91" s="3">
-        <v>-47371000</v>
+        <v>-443600</v>
       </c>
       <c r="I91" s="3">
-        <v>-43314000</v>
+        <v>-327600</v>
       </c>
       <c r="J91" s="3">
+        <v>-325800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-56276000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-44602000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-40183000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-47466000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-54255000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41155000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-299600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-302700</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4255,8 +4487,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4302,55 +4537,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-436500</v>
+        <v>-378600</v>
       </c>
       <c r="E94" s="3">
-        <v>-621000</v>
+        <v>-382100</v>
       </c>
       <c r="F94" s="3">
-        <v>-506600</v>
+        <v>-578300</v>
       </c>
       <c r="G94" s="3">
-        <v>-778500</v>
+        <v>-506200</v>
       </c>
       <c r="H94" s="3">
-        <v>-399300</v>
+        <v>-734100</v>
       </c>
       <c r="I94" s="3">
-        <v>-270700</v>
+        <v>-389000</v>
       </c>
       <c r="J94" s="3">
+        <v>-286800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-344100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-312300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-325800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-232700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-404700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-490000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-302300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-288600</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4368,55 +4609,59 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-490900</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
+        <v>505200</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G96" s="3">
-        <v>-496600</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>468300</v>
       </c>
       <c r="I96" s="3">
-        <v>-432600</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>458400</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-394300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-381900</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-339300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4462,8 +4707,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4509,8 +4757,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4556,145 +4807,157 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-271100</v>
+        <v>-544200</v>
       </c>
       <c r="E100" s="3">
-        <v>752500</v>
+        <v>-237300</v>
       </c>
       <c r="F100" s="3">
-        <v>-1574800</v>
+        <v>700700</v>
       </c>
       <c r="G100" s="3">
-        <v>-238500</v>
+        <v>-1573500</v>
       </c>
       <c r="H100" s="3">
-        <v>162900</v>
+        <v>-224900</v>
       </c>
       <c r="I100" s="3">
-        <v>537700</v>
+        <v>158700</v>
       </c>
       <c r="J100" s="3">
+        <v>569700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-832600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-45100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-409400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>253800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-875100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-362500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-469900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-189500</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>134300</v>
+        <v>39900</v>
       </c>
       <c r="E101" s="3">
-        <v>88400</v>
+        <v>120100</v>
       </c>
       <c r="F101" s="3">
-        <v>-53700</v>
+        <v>33000</v>
       </c>
       <c r="G101" s="3">
-        <v>42300</v>
+        <v>-87900</v>
       </c>
       <c r="H101" s="3">
-        <v>123300</v>
+        <v>49100</v>
       </c>
       <c r="I101" s="3">
-        <v>31100</v>
+        <v>131600</v>
       </c>
       <c r="J101" s="3">
+        <v>101800</v>
+      </c>
+      <c r="K101" s="3">
         <v>-82300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>45300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>120600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>82100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>30100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>13700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>84700</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>596600</v>
+        <v>-299800</v>
       </c>
       <c r="E102" s="3">
-        <v>768100</v>
+        <v>522400</v>
       </c>
       <c r="F102" s="3">
-        <v>-847900</v>
+        <v>715300</v>
       </c>
       <c r="G102" s="3">
-        <v>-152400</v>
+        <v>-847200</v>
       </c>
       <c r="H102" s="3">
-        <v>458000</v>
+        <v>-143700</v>
       </c>
       <c r="I102" s="3">
-        <v>820800</v>
+        <v>446200</v>
       </c>
       <c r="J102" s="3">
+        <v>869600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-732700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>70000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>148000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>205600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-555400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-298000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>295200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>556500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>CAJPY</t>
   </si>
@@ -656,85 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -759,32 +762,35 @@
       <c r="J8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L8" s="3">
         <v>8215900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6355100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6731900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5838900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6563900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6008300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6482200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6193500</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,32 +815,35 @@
       <c r="J9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L9" s="3">
         <v>4535700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3477500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3604300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3220100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3555900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3211100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3412700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3368400</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -859,32 +868,35 @@
       <c r="J10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L10" s="3">
         <v>3680200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2877600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3127600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2618800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3008000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2797200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3069500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -903,8 +915,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -929,32 +942,35 @@
       <c r="J12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L12" s="3">
         <v>608200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>478600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>503600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>473700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>524400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>524200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>521500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1003,8 +1019,11 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1029,8 +1048,8 @@
       <c r="J14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1053,8 +1072,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1079,8 +1101,8 @@
       <c r="J15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1103,8 +1125,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1120,8 +1145,9 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1146,32 +1172,35 @@
       <c r="J17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L17" s="3">
         <v>7524800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5835500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6068200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5333300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6046200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5584800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5914300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5674800</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1196,32 +1225,35 @@
       <c r="J18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L18" s="3">
         <v>691100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>519600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>663700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>505600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>517700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>423400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>567900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>518600</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1240,8 +1272,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1266,32 +1299,35 @@
       <c r="J20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L20" s="3">
         <v>166400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-13800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-87500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-54500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-24700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>149200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>63800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1316,32 +1352,35 @@
       <c r="J21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L21" s="3">
         <v>1285400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>857500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>958700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>811900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>904400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>964800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1044000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>860700</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1366,32 +1405,35 @@
       <c r="J22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L22" s="3">
         <v>2200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1416,32 +1458,35 @@
       <c r="J23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L23" s="3">
         <v>855300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>504500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>574200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>449500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>491600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>571900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>630400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1466,32 +1511,35 @@
       <c r="J24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L24" s="3">
         <v>215800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>139300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>149800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>118900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>55900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>180300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>156200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>128500</v>
       </c>
     </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1540,8 +1588,11 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
@@ -1566,32 +1617,35 @@
       <c r="J26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L26" s="3">
         <v>639500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>365200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>424400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>330600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>435700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>391700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>474200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
@@ -1616,32 +1670,35 @@
       <c r="J27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L27" s="3">
         <v>602400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>345300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>397800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>305300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>410800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>355600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>449400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1690,8 +1747,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1716,8 +1776,8 @@
       <c r="J29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1740,8 +1800,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1790,8 +1853,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1840,8 +1906,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -1866,32 +1935,35 @@
       <c r="J32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L32" s="3">
         <v>-166400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>13800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>87500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>54500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>24700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-149200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-63800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
@@ -1916,32 +1988,35 @@
       <c r="J33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L33" s="3">
         <v>602400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>345300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>397800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>305300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>410800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>355600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>449400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1990,8 +2065,11 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
@@ -2016,87 +2094,93 @@
       <c r="J35" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L35" s="3">
         <v>602400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>345300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>397800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>305300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>410800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>355600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>449400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2115,8 +2199,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2135,99 +2220,103 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3190200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3843200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3689700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3368600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2847000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3486500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3750100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3593500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2570900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2968600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3062100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2870900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2757600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3477000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3848200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3553000</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E42" s="3">
         <v>34800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>25700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>26000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>28900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>21200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>59200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>77400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>77900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>57600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>26600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>23200</v>
-      </c>
-      <c r="P42" s="3">
-        <v>700</v>
       </c>
       <c r="Q42" s="3">
         <v>700</v>
@@ -2235,358 +2324,382 @@
       <c r="R42" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>5446100</v>
+      </c>
+      <c r="E43" s="3">
         <v>5334500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5224400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5160500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5929300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5452400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5548400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5711500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5386100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3552900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3714700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3497900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3493500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3275800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3533700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3740600</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>5354500</v>
+      </c>
+      <c r="E44" s="3">
         <v>6210100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5672300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5916300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5653200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6118500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6211800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6460600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5739000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5639300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5379400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4868500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4469400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4587800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4330100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4379900</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F45" s="3">
         <v>1620600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1621500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>27700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1533500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2400800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2437300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2133500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2160500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2308900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2275900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2209100</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>15583800</v>
+      </c>
+      <c r="E46" s="3">
         <v>17114200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16232800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16092800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15777900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16479100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16916500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>17088000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15307000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14639500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14651200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13397400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12904200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13650100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13988700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13883200</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>720300</v>
+      </c>
+      <c r="E47" s="3">
         <v>556300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4624100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4562100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>556900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>497200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>522600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>515200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2511900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>450600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>477100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>481600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>515200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>556100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>509400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>497200</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8167500</v>
+      </c>
+      <c r="E48" s="3">
         <v>8631400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8018800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8307400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8669000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8203700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8469900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8812900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8185600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7442500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7849600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7659100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7812500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8166000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8367100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8429500</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>7573100</v>
+      </c>
+      <c r="E49" s="3">
         <v>9358900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>8692700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8994400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>9366700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8784200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8879000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9434400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8900700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8170600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8677100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8466100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8626300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9054200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9078800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9087100</v>
       </c>
     </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2635,8 +2748,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2685,58 +2801,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>2348200</v>
+      </c>
+      <c r="E52" s="3">
         <v>2073900</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="F52" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H52" s="3">
         <v>959900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1518000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1497400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1536000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1273000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3117500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3084000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2829500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2780400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2837000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2948300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2900900</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2785,58 +2907,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>36676300</v>
+      </c>
+      <c r="E54" s="3">
         <v>40035100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37568200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37956800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38425800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37620000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38533100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39559000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36178300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33820700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34738900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32833600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32638600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34263500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34892400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34797900</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2855,8 +2983,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2875,308 +3004,327 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>2227000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2474200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2331300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2407800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2198700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2303600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2493300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2742200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2527100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2507300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2467100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2333300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2326200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2363400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2294200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2332900</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>2291100</v>
+      </c>
+      <c r="E58" s="3">
         <v>4646400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3545700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3343600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2992000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4312100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3960400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3540200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2104300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1549000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>907400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>963500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>308400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2493700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2540900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3014200</v>
       </c>
     </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2561000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2285300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2449000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2156700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2534300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2437100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2682900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2539200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5062600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4489400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4570700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4265600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4653300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4839300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4883300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4769000</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>9835300</v>
+      </c>
+      <c r="E60" s="3">
         <v>12303200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10818300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10470600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10209700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11551200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11400100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11346100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9694000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8545700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7945200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7562300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7287900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9696400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9718400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10116000</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1929100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1393500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1324800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1367400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>677900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>614700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>624100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>646100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1150400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1215500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1192900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1234900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>42700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>41700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>670700</v>
+      </c>
+      <c r="E62" s="3">
         <v>681600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>675300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>668400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>450500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>646900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>679800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>729600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2689000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2724700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2906500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2842100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2829600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3188900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3366400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3458200</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3225,8 +3373,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3275,8 +3426,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3325,58 +3479,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>13491900</v>
+      </c>
+      <c r="E66" s="3">
         <v>15541300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13903400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13632800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12846500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13949300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14014300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14127800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14075200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13898400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13620300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13099800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12895800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14507600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14713500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15171700</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3395,8 +3555,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3445,8 +3606,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3495,8 +3659,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3545,8 +3712,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3595,58 +3765,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>24682400</v>
+      </c>
+      <c r="E72" s="3">
         <v>27495400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24509400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25477800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>27403500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25322900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>26213500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28019300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26477600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>23251300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>24615100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>23858000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>24773600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>25558200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>26037900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>25588500</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3695,8 +3871,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3745,8 +3924,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3795,58 +3977,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>21500300</v>
+      </c>
+      <c r="E76" s="3">
         <v>22727100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22047600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22651100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>23786700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22035100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22833300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>23640100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22103000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19922400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21118600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19733900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19742800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19755900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>20178900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19626200</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3895,63 +4083,69 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
@@ -3976,32 +4170,35 @@
       <c r="J81" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L81" s="3">
         <v>602400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>345300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>397800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>305300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>410800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>355600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>449400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4020,58 +4217,62 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E83" s="3">
         <v>421200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>406200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>394700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>457000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>381000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>417600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>447600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>427900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>351700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>382500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>360900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>411300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>392200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>412300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>374000</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4120,8 +4321,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4170,8 +4374,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4220,8 +4427,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4270,8 +4480,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4320,58 +4533,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1550900</v>
+      </c>
+      <c r="E89" s="3">
         <v>844800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1024200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>510500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1286200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>775500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>556400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>553700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>526300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>382200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>762700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>102400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>694300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>557800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1053700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>950000</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4390,58 +4609,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-407400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-406100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-386000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-348200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-520400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-443600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-327600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-325800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-56276000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-44602000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-40183000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-47466000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-54255000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41155000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-299600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-302700</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4490,8 +4713,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4540,58 +4766,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-598800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-378600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-382100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-578300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-506200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-734100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-389000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-286800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-344100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-312300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-325800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-232700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-404700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-490000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-302300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-288600</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4610,58 +4842,62 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>505200</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="F96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>468300</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>458400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-394300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-381900</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-339300</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4710,8 +4946,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4760,8 +4999,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4810,154 +5052,166 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1372800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-544200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-237300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1573500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-224900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>158700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>569700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-832600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-45100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-409400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>253800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-875100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-362500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-469900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-189500</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="E101" s="3">
         <v>39900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>120100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>33000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-87900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>49100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>131600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>101800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-82300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>45300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>120600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>82100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>30100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>13700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>84700</v>
       </c>
     </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-311800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-299800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>522400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>715300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-847200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-143700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>446200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>869600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-732700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>70000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>148000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>205600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-555400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-298000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>295200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>556500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
   <si>
     <t>CAJPY</t>
   </si>
@@ -656,88 +656,92 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,32 +769,35 @@
       <c r="K8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M8" s="3">
         <v>8215900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6355100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6731900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5838900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6563900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6008300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6482200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6193500</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -818,32 +825,35 @@
       <c r="K9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M9" s="3">
         <v>4535700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3477500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3604300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3220100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3555900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3211100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3412700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3368400</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -871,32 +881,35 @@
       <c r="K10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M10" s="3">
         <v>3680200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2877600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3127600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2618800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3008000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2797200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3069500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -916,8 +929,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,32 +959,35 @@
       <c r="K12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M12" s="3">
         <v>608200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>478600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>503600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>473700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>524400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>524200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>521500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1022,8 +1039,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1051,8 +1071,8 @@
       <c r="K14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1075,8 +1095,11 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1104,8 +1127,8 @@
       <c r="K15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1128,8 +1151,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1146,8 +1172,9 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1175,32 +1202,35 @@
       <c r="K17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M17" s="3">
         <v>7524800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5835500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6068200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5333300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6046200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5584800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5914300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5674800</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1228,32 +1258,35 @@
       <c r="K18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M18" s="3">
         <v>691100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>519600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>663700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>505600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>517700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>423400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>567900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>518600</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1273,8 +1306,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1302,32 +1336,35 @@
       <c r="K20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M20" s="3">
         <v>166400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-13800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-87500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-54500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>149200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>63800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1355,32 +1392,35 @@
       <c r="K21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M21" s="3">
         <v>1285400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>857500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>958700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>811900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>904400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>964800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1044000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>860700</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1408,32 +1448,35 @@
       <c r="K22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M22" s="3">
         <v>2200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1461,32 +1504,35 @@
       <c r="K23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M23" s="3">
         <v>855300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>504500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>574200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>449500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>491600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>571900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>630400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1514,32 +1560,35 @@
       <c r="K24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M24" s="3">
         <v>215800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>139300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>149800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>118900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>55900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>180300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>156200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>128500</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1591,8 +1640,11 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
@@ -1620,32 +1672,35 @@
       <c r="K26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M26" s="3">
         <v>639500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>365200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>424400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>330600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>435700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>391700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>474200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
@@ -1673,32 +1728,35 @@
       <c r="K27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M27" s="3">
         <v>602400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>345300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>397800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>305300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>410800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>355600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>449400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1750,8 +1808,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1779,8 +1840,8 @@
       <c r="K29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -1803,8 +1864,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1856,8 +1920,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1909,8 +1976,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -1938,32 +2008,35 @@
       <c r="K32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M32" s="3">
         <v>-166400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>13800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>87500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>54500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>24700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-149200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-63800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
@@ -1991,32 +2064,35 @@
       <c r="K33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M33" s="3">
         <v>602400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>345300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>397800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>305300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>410800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>355600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>449400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2068,8 +2144,11 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
@@ -2097,90 +2176,96 @@
       <c r="K35" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M35" s="3">
         <v>602400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>345300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>397800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>305300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>410800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>355600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>449400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2200,8 +2285,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2221,105 +2307,109 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>4655500</v>
+      </c>
+      <c r="E41" s="3">
         <v>3190200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3843200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3689700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3368600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2847000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3486500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3750100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3593500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2570900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2968600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3062100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2870900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2757600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3477000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3848200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3553000</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E42" s="3">
         <v>30400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>34800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>28900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>21200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>59200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>77400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>77900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>57600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>26600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>23200</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>700</v>
       </c>
       <c r="R42" s="3">
         <v>700</v>
@@ -2327,379 +2417,403 @@
       <c r="S42" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>5446100</v>
+        <v>5160600</v>
       </c>
       <c r="E43" s="3">
+        <v>5739000</v>
+      </c>
+      <c r="F43" s="3">
         <v>5334500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5224400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5160500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5929300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5452400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5548400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5711500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5386100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3552900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3714700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3497900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3493500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3275800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3533700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3740600</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>5828600</v>
+      </c>
+      <c r="E44" s="3">
         <v>5354500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6210100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5672300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5916300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5653200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6118500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6211800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6460600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5739000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5639300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5379400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4868500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4469400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4587800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4330100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4379900</v>
       </c>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="E45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G45" s="3">
         <v>1620600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1621500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1533500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2400800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2437300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2133500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2160500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2308900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2275900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2209100</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>17303100</v>
+      </c>
+      <c r="E46" s="3">
         <v>15583800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>17114200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16232800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16092800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15777900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16479100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16916500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>17088000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15307000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14639500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14651200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13397400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12904200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13650100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13988700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13883200</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>755500</v>
+      </c>
+      <c r="E47" s="3">
         <v>720300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>556300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4624100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4562100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>556900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>497200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>522600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>515200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2511900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>450600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>477100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>481600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>515200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>556100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>509400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>497200</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8483100</v>
+      </c>
+      <c r="E48" s="3">
         <v>8167500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8631400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8018800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8307400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8669000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8203700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8469900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8812900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8185600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7442500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7849600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7659100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7812500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8166000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8367100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8429500</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>7911900</v>
+      </c>
+      <c r="E49" s="3">
         <v>7573100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9358900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8692700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8994400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9366700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8784200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8879000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9434400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8900700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8170600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8677100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8466100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8626300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9054200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9078800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9087100</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2751,8 +2865,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2804,61 +2921,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>2348200</v>
+        <v>2531200</v>
       </c>
       <c r="E52" s="3">
+        <v>1701300</v>
+      </c>
+      <c r="F52" s="3">
         <v>2073900</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I52" s="3">
         <v>959900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1518000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1497400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1536000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1273000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3117500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3084000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2829500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2780400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2837000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2948300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2900900</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2910,61 +3033,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>39227000</v>
+      </c>
+      <c r="E54" s="3">
         <v>36676300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>40035100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37568200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37956800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38425800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37620000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38533100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>39559000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36178300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33820700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34738900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32833600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32638600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>34263500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34892400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34797900</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2984,8 +3113,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3005,326 +3135,345 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>2386300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2227000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2474200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2331300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2407800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2198700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2303600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2493300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2742200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2527100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2507300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2467100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2333300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2326200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2363400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2294200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2332900</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>5527100</v>
+      </c>
+      <c r="E58" s="3">
         <v>2291100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4646400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3545700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3343600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2992000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4312100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3960400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3540200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2104300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1549000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>907400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>963500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>308400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2493700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2540900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3014200</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>2561000</v>
+        <v>2321700</v>
       </c>
       <c r="E59" s="3">
+        <v>2711700</v>
+      </c>
+      <c r="F59" s="3">
         <v>2285300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2449000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2156700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2534300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2437100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2682900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2539200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5062600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4489400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4570700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4265600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4653300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4839300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4883300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4769000</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>12913100</v>
+      </c>
+      <c r="E60" s="3">
         <v>9835300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>12303200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10818300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10470600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10209700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11551200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11400100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11346100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9694000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8545700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7945200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7562300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7287900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9696400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9718400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10116000</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1313200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1929100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1393500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1324800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1367400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>677900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>614700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>624100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>646100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>17200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1150400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1215500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1192900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1234900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>42700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>41700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>670700</v>
+        <v>671900</v>
       </c>
       <c r="E62" s="3">
+        <v>433100</v>
+      </c>
+      <c r="F62" s="3">
         <v>681600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>675300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>668400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>450500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>646900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>679800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>729600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2689000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2724700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2906500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2842100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2829600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3188900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3366400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3458200</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3376,8 +3525,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3429,8 +3581,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3482,61 +3637,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>15987500</v>
+      </c>
+      <c r="E66" s="3">
         <v>13491900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>15541300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13903400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13632800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12846500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13949300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14014300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14127800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14075200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13898400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13620300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13099800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12895800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14507600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14713500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15171700</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3556,8 +3717,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3609,8 +3771,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3662,8 +3827,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3715,8 +3883,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3768,61 +3939,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>25892000</v>
+      </c>
+      <c r="E72" s="3">
         <v>24682400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>27495400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>24509400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25477800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27403500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25322900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26213500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28019300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>26477600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>23251300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>24615100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>23858000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>24773600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>25558200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>26037900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>25588500</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3874,8 +4051,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3927,8 +4107,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3980,61 +4163,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>21476500</v>
+      </c>
+      <c r="E76" s="3">
         <v>21500300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>22727100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22047600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22651100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23786700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22035100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22833300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>23640100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22103000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>19922400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21118600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19733900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19742800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19755900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>20178900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19626200</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4086,66 +4275,72 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
@@ -4173,32 +4368,35 @@
       <c r="K81" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="M81" s="3">
         <v>602400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>345300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>397800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>305300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>410800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>355600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>449400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4218,61 +4416,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>360000</v>
+      </c>
+      <c r="E83" s="3">
         <v>24900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>421200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>406200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>394700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>457000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>381000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>417600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>447600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>427900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>351700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>382500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>360900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>411300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>392200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>412300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>374000</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4324,8 +4526,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4377,8 +4582,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4430,8 +4638,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4483,8 +4694,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4536,61 +4750,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>480400</v>
+      </c>
+      <c r="E89" s="3">
         <v>1550900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>844800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1024200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>510500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1286200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>775500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>556400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>553700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>526300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>382200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>762700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>102400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>694300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>557800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1053700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>950000</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4610,61 +4830,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-343100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-407400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-406100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-386000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-348200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-520400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-443600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-327600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-325800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-56276000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-44602000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-40183000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-47466000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-54255000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-41155000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-299600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-302700</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4716,8 +4940,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4769,61 +4996,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-345900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-598800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-378600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-382100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-578300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-506200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-734100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-389000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-286800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-344100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-312300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-325800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-232700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-404700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-490000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-302300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-288600</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4843,61 +5076,65 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>504300</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>505200</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>468300</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>458400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-394300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-381900</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-339300</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4949,8 +5186,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5002,8 +5242,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5055,163 +5298,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>1252900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1372800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-544200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-237300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1573500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-224900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>158700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>569700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-832600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-45100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-409400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>253800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-875100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-362500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-469900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-189500</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>82400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-53700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>39900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>120100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>33000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-87900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>49100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>131600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>101800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-82300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>45300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>120600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>82100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>30100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>13700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>84700</v>
       </c>
     </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>1306100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-311800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-299800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>522400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>715300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-847200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-143700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>446200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>869600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-732700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>70000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>148000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>205600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-555400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-298000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>295200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>556500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>CAJPY</t>
   </si>
@@ -656,92 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -772,32 +776,35 @@
       <c r="L8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N8" s="3">
         <v>8215900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6355100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6731900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5838900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6563900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6008300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6482200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6193500</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -828,32 +835,35 @@
       <c r="L9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N9" s="3">
         <v>4535700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3477500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3604300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3220100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3555900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3211100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3412700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3368400</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -884,32 +894,35 @@
       <c r="L10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N10" s="3">
         <v>3680200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2877600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3127600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2618800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3008000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2797200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>3069500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -930,8 +943,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -962,32 +976,35 @@
       <c r="L12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N12" s="3">
         <v>608200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>478600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>503600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>473700</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>524400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>524200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>521500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1042,8 +1059,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1074,8 +1094,8 @@
       <c r="L14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1098,8 +1118,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1130,8 +1153,8 @@
       <c r="L15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1154,8 +1177,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1173,8 +1199,9 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1205,32 +1232,35 @@
       <c r="L17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N17" s="3">
         <v>7524800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5835500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6068200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5333300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6046200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5584800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5914300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5674800</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1261,32 +1291,35 @@
       <c r="L18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N18" s="3">
         <v>691100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>519600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>663700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>505600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>517700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>423400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>567900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>518600</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1307,8 +1340,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1339,32 +1373,35 @@
       <c r="L20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N20" s="3">
         <v>166400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-87500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-54500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-24700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>149200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>63800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1395,32 +1432,35 @@
       <c r="L21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N21" s="3">
         <v>1285400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>857500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>958700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>811900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>904400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>964800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1044000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>860700</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1451,32 +1491,35 @@
       <c r="L22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N22" s="3">
         <v>2200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1507,32 +1550,35 @@
       <c r="L23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N23" s="3">
         <v>855300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>504500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>574200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>449500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>491600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>571900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>630400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1563,32 +1609,35 @@
       <c r="L24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N24" s="3">
         <v>215800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>139300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>149800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>118900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>55900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>180300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>156200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>128500</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1643,8 +1692,11 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
@@ -1675,32 +1727,35 @@
       <c r="L26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N26" s="3">
         <v>639500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>365200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>424400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>330600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>435700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>391700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>474200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
@@ -1731,32 +1786,35 @@
       <c r="L27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N27" s="3">
         <v>602400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>345300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>397800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>305300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>410800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>355600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>449400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1811,8 +1869,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1843,8 +1904,8 @@
       <c r="L29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -1867,8 +1928,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1923,8 +1987,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1979,8 +2046,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -2011,32 +2081,35 @@
       <c r="L32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N32" s="3">
         <v>-166400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>87500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>54500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>24700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-149200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-63800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
@@ -2067,32 +2140,35 @@
       <c r="L33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N33" s="3">
         <v>602400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>345300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>397800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>305300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>410800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>355600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>449400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2147,8 +2223,11 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
@@ -2179,93 +2258,99 @@
       <c r="L35" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N35" s="3">
         <v>602400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>345300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>397800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>305300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>410800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>355600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>449400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2286,8 +2371,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2308,111 +2394,115 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>4655500</v>
-      </c>
-      <c r="E41" s="3">
+        <v>4957000</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F41" s="3">
         <v>3190200</v>
       </c>
-      <c r="F41" s="3">
-        <v>3843200</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="3">
         <v>3689700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3368600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2847000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3486500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3750100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3593500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2570900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2968600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3062100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2870900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2757600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3477000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3848200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3553000</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>31800</v>
+        <v>47200</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>30400</v>
       </c>
-      <c r="F42" s="3">
-        <v>34800</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>25700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>26000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>27100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>28900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>59200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>77400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>77900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>57600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>26600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>23200</v>
-      </c>
-      <c r="R42" s="3">
-        <v>700</v>
       </c>
       <c r="S42" s="3">
         <v>700</v>
@@ -2420,400 +2510,424 @@
       <c r="T42" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>5160600</v>
-      </c>
-      <c r="E43" s="3">
+        <v>5422300</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F43" s="3">
         <v>5739000</v>
       </c>
-      <c r="F43" s="3">
-        <v>5334500</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" s="3">
         <v>5224400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5160500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5929300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5452400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5548400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5711500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5386100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3552900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3714700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3497900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3493500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3275800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3533700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3740600</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>5828600</v>
-      </c>
-      <c r="E44" s="3">
+        <v>6095700</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" s="3">
         <v>5354500</v>
       </c>
-      <c r="F44" s="3">
-        <v>6210100</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H44" s="3">
         <v>5672300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5916300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5653200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6118500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6211800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6460600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5739000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5639300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5379400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4868500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4469400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4587800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4330100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4379900</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>1812300</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F45" s="3">
         <v>1400</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" s="3">
         <v>1620600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1621500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1533500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2400800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2437300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2133500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2160500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2308900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2275900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2209100</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>17303100</v>
-      </c>
-      <c r="E46" s="3">
+        <v>18334500</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F46" s="3">
         <v>15583800</v>
       </c>
-      <c r="F46" s="3">
-        <v>17114200</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H46" s="3">
         <v>16232800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16092800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15777900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16479100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16916500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>17088000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15307000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14639500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14651200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13397400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>12904200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13650100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13988700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13883200</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>755500</v>
-      </c>
-      <c r="E47" s="3">
+        <v>5914900</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="3">
         <v>720300</v>
       </c>
-      <c r="F47" s="3">
-        <v>556300</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" s="3">
         <v>4624100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4562100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>556900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>497200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>522600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>515200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2511900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>450600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>477100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>481600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>515200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>556100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>509400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>497200</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>8483100</v>
-      </c>
-      <c r="E48" s="3">
+        <v>8870000</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F48" s="3">
         <v>8167500</v>
       </c>
-      <c r="F48" s="3">
-        <v>8631400</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H48" s="3">
         <v>8018800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8307400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8669000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8203700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8469900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8812900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8185600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>7442500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7849600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7659100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7812500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8166000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8367100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8429500</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>7911900</v>
-      </c>
-      <c r="E49" s="3">
+        <v>8259600</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F49" s="3">
         <v>7573100</v>
       </c>
-      <c r="F49" s="3">
-        <v>9358900</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H49" s="3">
         <v>8692700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8994400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9366700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8784200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8879000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9434400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>8900700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8170600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8677100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8466100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8626300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9054200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9078800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9087100</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2868,8 +2982,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2924,64 +3041,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="3">
-        <v>2531200</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" s="3">
         <v>1701300</v>
       </c>
-      <c r="F52" s="3">
-        <v>2073900</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>91</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J52" s="3">
         <v>959900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1518000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1497400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1536000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1273000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3117500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3084000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2829500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2780400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2837000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2948300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2900900</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3036,64 +3159,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>39227000</v>
-      </c>
-      <c r="E54" s="3">
+        <v>41379000</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F54" s="3">
         <v>36676300</v>
       </c>
-      <c r="F54" s="3">
-        <v>40035100</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H54" s="3">
         <v>37568200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>37956800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38425800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>37620000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38533100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>39559000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>36178300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>33820700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>34738900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>32833600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32638600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>34263500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34892400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34797900</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3114,8 +3243,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3136,344 +3266,363 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>2386300</v>
-      </c>
-      <c r="E57" s="3">
+        <v>2403100</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" s="3">
         <v>2227000</v>
       </c>
-      <c r="F57" s="3">
-        <v>2474200</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H57" s="3">
         <v>2331300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2407800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2198700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2303600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2493300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2742200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2527100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2507300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2467100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2333300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2326200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2363400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2294200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2332900</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>5527100</v>
-      </c>
-      <c r="E58" s="3">
+        <v>5046000</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F58" s="3">
         <v>2291100</v>
       </c>
-      <c r="F58" s="3">
-        <v>4646400</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H58" s="3">
         <v>3545700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3343600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2992000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4312100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3960400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3540200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2104300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1549000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>907400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>963500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>308400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2493700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2540900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3014200</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>2321700</v>
-      </c>
-      <c r="E59" s="3">
+        <v>2529400</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F59" s="3">
         <v>2711700</v>
       </c>
-      <c r="F59" s="3">
-        <v>2285300</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H59" s="3">
         <v>2449000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2156700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2534300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2437100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2682900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2539200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5062600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4489400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4570700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4265600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4653300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4839300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4883300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4769000</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>12913100</v>
-      </c>
-      <c r="E60" s="3">
+        <v>12705800</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F60" s="3">
         <v>9835300</v>
       </c>
-      <c r="F60" s="3">
-        <v>12303200</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H60" s="3">
         <v>10818300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10470600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10209700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11551200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11400100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11346100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9694000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8545700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7945200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7562300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7287900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9696400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9718400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10116000</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1313200</v>
+        <v>2705300</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>1929100</v>
       </c>
-      <c r="F61" s="3">
-        <v>1393500</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>1324800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1367400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>677900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>614700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>624100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>646100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>17200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1150400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1215500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1192900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1234900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>42700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>41700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>671900</v>
-      </c>
-      <c r="E62" s="3">
+        <v>692000</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F62" s="3">
         <v>433100</v>
       </c>
-      <c r="F62" s="3">
-        <v>681600</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62" s="3">
         <v>675300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>668400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>450500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>646900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>679800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>729600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2689000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2724700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2906500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2842100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2829600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3188900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3366400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3458200</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3528,8 +3677,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3584,8 +3736,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3640,64 +3795,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>15987500</v>
-      </c>
-      <c r="E66" s="3">
+        <v>17251300</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F66" s="3">
         <v>13491900</v>
       </c>
-      <c r="F66" s="3">
-        <v>15541300</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H66" s="3">
         <v>13903400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>13632800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12846500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13949300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14014300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14127800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14075200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13898400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13620300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13099800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12895800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14507600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14713500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15171700</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3718,8 +3879,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3774,8 +3936,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3830,8 +3995,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3886,8 +4054,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3942,64 +4113,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>25892000</v>
-      </c>
-      <c r="E72" s="3">
+        <v>27453600</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F72" s="3">
         <v>24682400</v>
       </c>
-      <c r="F72" s="3">
-        <v>27495400</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H72" s="3">
         <v>24509400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>25477800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>27403500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>25322900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>26213500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28019300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>26477600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>23251300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>24615100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>23858000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>24773600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>25558200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>26037900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>25588500</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4054,8 +4231,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4110,8 +4290,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4166,64 +4349,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>21476500</v>
-      </c>
-      <c r="E76" s="3">
+        <v>22251500</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F76" s="3">
         <v>21500300</v>
       </c>
-      <c r="F76" s="3">
-        <v>22727100</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H76" s="3">
         <v>22047600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22651100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>23786700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22035100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22833300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>23640100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>22103000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>19922400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21118600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19733900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19742800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19755900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>20178900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19626200</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4278,69 +4467,75 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
@@ -4371,32 +4566,35 @@
       <c r="L81" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N81" s="3">
         <v>602400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>345300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>397800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>305300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>410800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>355600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>449400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4417,64 +4615,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>366100</v>
+      </c>
+      <c r="E83" s="3">
         <v>360000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>24900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>421200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>406200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>394700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>457000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>381000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>417600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>447600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>427900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>351700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>382500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>360900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>411300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>392200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>412300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>374000</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4529,8 +4731,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4585,8 +4790,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4641,8 +4849,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4697,8 +4908,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4753,64 +4967,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>480400</v>
-      </c>
-      <c r="E89" s="3">
+        <v>602700</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F89" s="3">
         <v>1550900</v>
       </c>
-      <c r="F89" s="3">
-        <v>844800</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H89" s="3">
         <v>1024200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>510500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1286200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>775500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>556400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>553700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>526300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>382200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>762700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>102400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>694300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>557800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1053700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>950000</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4831,64 +5051,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-343100</v>
-      </c>
-      <c r="E91" s="3">
+        <v>-470200</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F91" s="3">
         <v>-407400</v>
       </c>
-      <c r="F91" s="3">
-        <v>-406100</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="G91" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H91" s="3">
         <v>-386000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-348200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-520400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-443600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-327600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-325800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-56276000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-44602000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-40183000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-47466000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-54255000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-41155000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-299600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-302700</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4943,8 +5167,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4999,64 +5226,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-345900</v>
-      </c>
-      <c r="E94" s="3">
+        <v>-501600</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F94" s="3">
         <v>-598800</v>
       </c>
-      <c r="F94" s="3">
-        <v>-378600</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H94" s="3">
         <v>-382100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-578300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-506200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-734100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-389000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-286800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-344100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-312300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-325800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-232700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-404700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-490000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-302300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-288600</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5077,19 +5310,20 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3">
-        <v>504300</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="F96" s="3">
-        <v>505200</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>91</v>
@@ -5097,44 +5331,47 @@
       <c r="H96" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>468300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>458400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-394300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-381900</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-339300</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5189,8 +5426,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5245,8 +5485,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5301,172 +5544,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>1252900</v>
-      </c>
-      <c r="E100" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1372800</v>
       </c>
-      <c r="F100" s="3">
-        <v>-544200</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H100" s="3">
         <v>-237300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1573500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-224900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>158700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>569700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-832600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-45100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-409400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>253800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-875100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-362500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-469900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-189500</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>117600</v>
+      </c>
+      <c r="E101" s="3">
         <v>82400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-53700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>39900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>120100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>33000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-87900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>49100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>131600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>101800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-82300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>45300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>120600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>82100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>30100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>13700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>84700</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>1306100</v>
+        <v>125000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-311800</v>
       </c>
-      <c r="F102" s="3">
-        <v>-299800</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>522400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>715300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-847200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-143700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>446200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>869600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-732700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>70000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>148000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>205600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-555400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-298000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>295200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>556500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>CAJPY</t>
   </si>
@@ -5317,17 +5317,17 @@
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>91</v>
+      <c r="D96" s="3">
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>91</v>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>457100</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>

--- a/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAJPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="92">
   <si>
     <t>CAJPY</t>
   </si>
@@ -656,97 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -780,32 +784,35 @@
       <c r="M8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O8" s="3">
         <v>8215900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6355100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6731900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5838900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6563900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6008300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6482200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6193500</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -839,32 +846,35 @@
       <c r="M9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="3">
         <v>4535700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3477500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3604300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3220100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3555900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3211100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3412700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3368400</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -898,32 +908,35 @@
       <c r="M10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O10" s="3">
         <v>3680200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2877600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3127600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2618800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3008000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2797200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3069500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2825000</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -945,8 +958,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -980,32 +994,35 @@
       <c r="M12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O12" s="3">
         <v>608200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>478600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>503600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>473700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>524400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>524200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>521500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>495100</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1063,8 +1080,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1098,8 +1118,8 @@
       <c r="M14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1122,8 +1142,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1157,8 +1180,8 @@
       <c r="M15" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1181,8 +1204,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,8 +1227,9 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1236,32 +1263,35 @@
       <c r="M17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O17" s="3">
         <v>7524800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5835500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6068200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5333300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6046200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5584800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5914300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5674800</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1295,32 +1325,35 @@
       <c r="M18" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O18" s="3">
         <v>691100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>519600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>663700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>505600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>517700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>423400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>567900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>518600</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1342,8 +1375,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,32 +1411,35 @@
       <c r="M20" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O20" s="3">
         <v>166400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-13800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-87500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-54500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-24700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>149200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>63800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1436,32 +1473,35 @@
       <c r="M21" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O21" s="3">
         <v>1285400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>857500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>958700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>811900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>904400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>964800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1044000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>860700</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -1495,32 +1535,35 @@
       <c r="M22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O22" s="3">
         <v>2200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1200</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
@@ -1554,32 +1597,35 @@
       <c r="M23" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O23" s="3">
         <v>855300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>504500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>574200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>449500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>491600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>571900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>630400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
@@ -1613,32 +1659,35 @@
       <c r="M24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O24" s="3">
         <v>215800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>139300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>149800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>118900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>55900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>180300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>156200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>128500</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1696,8 +1745,11 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
@@ -1731,32 +1783,35 @@
       <c r="M26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O26" s="3">
         <v>639500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>365200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>424400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>330600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>435700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>391700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>474200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
@@ -1790,32 +1845,35 @@
       <c r="M27" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O27" s="3">
         <v>602400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>345300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>397800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>305300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>410800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>355600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>449400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1873,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1908,8 +1969,8 @@
       <c r="M29" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -1932,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1991,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -2050,8 +2117,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
@@ -2085,32 +2155,35 @@
       <c r="M32" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O32" s="3">
         <v>-166400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>13800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>87500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>54500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>24700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-149200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-63800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>32000</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
@@ -2144,32 +2217,35 @@
       <c r="M33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O33" s="3">
         <v>602400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>345300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>397800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>305300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>410800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>355600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>449400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -2227,8 +2303,11 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
@@ -2262,96 +2341,102 @@
       <c r="M35" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O35" s="3">
         <v>602400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>345300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>397800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>305300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>410800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>355600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>449400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2373,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2396,117 +2482,121 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3737400</v>
+      </c>
+      <c r="E41" s="3">
         <v>4957000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3190200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3689700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3368600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2847000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3486500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3750100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3486500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3750100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3593500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2570900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2968600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3062100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2870900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2757600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3477000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3848200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3553000</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>206900</v>
+      </c>
+      <c r="E42" s="3">
         <v>47200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>30400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>25700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>26000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>28900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>21200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>28900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>59200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>77400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>77900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>57600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>26600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>23200</v>
-      </c>
-      <c r="S42" s="3">
-        <v>700</v>
       </c>
       <c r="T42" s="3">
         <v>700</v>
@@ -2514,421 +2604,445 @@
       <c r="U42" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>6027500</v>
+      </c>
+      <c r="E43" s="3">
         <v>5422300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5739000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5224400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>5160500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5929300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5452400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5548400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5452400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5548400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5711500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5386100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3552900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3714700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3497900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3493500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3275800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3533700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3740600</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>5360400</v>
+      </c>
+      <c r="E44" s="3">
         <v>6095700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5354500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5672300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5916300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5653200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6118500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6211800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6118500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6211800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6460600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5739000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5639300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5379400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4868500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4469400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4587800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4330100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4379900</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1812300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1620600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1621500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>27700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1533500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2400800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2437300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2133500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2160500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2308900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2275900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2209100</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>16691500</v>
+      </c>
+      <c r="E46" s="3">
         <v>18334500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15583800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16232800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16092800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15777900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16479100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16916500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16479100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16916500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>17088000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15307000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14639500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14651200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13397400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12904200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13650100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13988700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13883200</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>660800</v>
+      </c>
+      <c r="E47" s="3">
         <v>5914900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>720300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4624100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4562100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>556900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>497200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>522600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>497200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>522600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>515200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2511900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>450600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>477100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>481600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>515200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>556100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>509400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>497200</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8404200</v>
+      </c>
+      <c r="E48" s="3">
         <v>8870000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8167500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8018800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>8307400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8669000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8203700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>8469900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>8203700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8469900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8812900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8185600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>7442500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>7849600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7659100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7812500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8166000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8367100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8429500</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>7943600</v>
+      </c>
+      <c r="E49" s="3">
         <v>8259600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>7573100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8692700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8994400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9366700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8784200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8879000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>8784200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>8879000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9434400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>8900700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>8170600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8677100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8466100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8626300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9054200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>9078800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>9087100</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2986,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -3045,67 +3162,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>2637200</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F52" s="3">
         <v>1701300</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I52" s="3">
         <v>959900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1518000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1497400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1518000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1497400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1536000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1273000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3117500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3084000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2829500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2780400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2837000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2948300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2900900</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -3163,67 +3286,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>39129600</v>
+      </c>
+      <c r="E54" s="3">
         <v>41379000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>36676300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37568200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37956800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38425800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>37620000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38533100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>37620000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>38533100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39559000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>36178300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>33820700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>34738900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>32833600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32638600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>34263500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>34892400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>34797900</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -3245,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -3268,362 +3398,381 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>1982500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2403100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2227000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2331300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2407800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2198700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2303600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2493300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2303600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2493300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2742200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2527100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2507300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2467100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2333300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2326200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2363400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2294200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2332900</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>3534900</v>
+      </c>
+      <c r="E58" s="3">
         <v>5046000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2291100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3545700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3343600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2992000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4312100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3960400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4312100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3960400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3540200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2104300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1549000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>907400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>963500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>308400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2493700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2540900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3014200</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>2496300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2529400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2711700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2449000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2156700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2534300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2437100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2682900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2437100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2682900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2539200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5062600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4489400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4570700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4265600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4653300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4839300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4883300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4769000</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>10868600</v>
+      </c>
+      <c r="E60" s="3">
         <v>12705800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9835300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10818300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10470600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10209700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11551200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11400100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11551200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11400100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11346100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9694000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8545700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7945200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7562300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7287900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9696400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9718400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10116000</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>2499700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2705300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1929100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1324800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1367400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>677900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>614700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>624100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>614700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>624100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>646100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>17200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1150400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1215500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1192900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1234900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>42700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>41700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>321600</v>
+      </c>
+      <c r="E62" s="3">
         <v>692000</v>
       </c>
-      <c r="E62" s="3">
-        <v>433100</v>
-      </c>
       <c r="F62" s="3">
+        <v>311600</v>
+      </c>
+      <c r="G62" s="3">
         <v>675300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>668400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>450500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>646900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>679800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>646900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>679800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>729600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2689000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2724700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2906500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2842100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2829600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3188900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3366400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3458200</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3681,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3740,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3799,67 +3954,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>15058000</v>
+      </c>
+      <c r="E66" s="3">
         <v>17251300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>13491900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13903400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13632800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12846500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>13949300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>14014300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13949300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14014300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14127800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14075200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13898400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13620300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13099800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12895800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14507600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14713500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15171700</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3881,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3940,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3999,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -4058,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -4117,67 +4288,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>25926200</v>
+      </c>
+      <c r="E72" s="3">
         <v>27453600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24682400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>24509400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25477800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>27403500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>25322900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>26213500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>25322900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>26213500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28019300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>26477600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>23251300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>24615100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>23858000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>24773600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>25558200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>26037900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>25588500</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -4235,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -4294,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -4353,67 +4536,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>22270900</v>
+      </c>
+      <c r="E76" s="3">
         <v>22251500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>21500300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>22047600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>22651100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>23786700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>22035100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22833300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22035100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22833300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>23640100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22103000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>19922400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21118600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19733900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>19742800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>19755900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>20178900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>19626200</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -4471,72 +4660,78 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
@@ -4570,32 +4765,35 @@
       <c r="M81" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="O81" s="3">
         <v>602400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>345300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>397800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>305300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>410800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>355600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>449400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -4617,67 +4815,71 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>360000</v>
+      </c>
+      <c r="E83" s="3">
         <v>24900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>421200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>406200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>394700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>457000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>381000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>417600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>381000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>417600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>447600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>427900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>351700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>382500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>360900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>411300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>392200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>412300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>374000</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -4735,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4794,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4853,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4912,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4971,67 +5185,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>1226800</v>
+      </c>
+      <c r="E89" s="3">
         <v>602700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1550900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1024200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>510500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1286200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>775500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>556400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>775500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>556400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>553700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>526300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>382200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>762700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>102400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>694300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>557800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1053700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>950000</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -5053,67 +5273,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-504000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-470200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-407400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-386000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-348200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-520400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-443600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-327600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-443600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-327600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-325800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-56276000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-44602000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-40183000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-47466000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-54255000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-41155000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-299600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-302700</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -5171,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -5230,67 +5457,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-312700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-501600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-598800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-382100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-578300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-506200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-734100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-389000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-734100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-389000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-286800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-344100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-312300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-325800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-232700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-404700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-490000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-302300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-288600</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -5312,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
@@ -5327,52 +5561,55 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>457100</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>468300</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>468300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>458400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-394300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-381900</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-339300</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-307500</v>
       </c>
     </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -5430,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -5489,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -5548,181 +5791,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1771600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1372800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-237300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1573500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-224900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>158700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-224900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>158700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>569700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-832600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-45100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-409400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>253800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-875100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-362500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-469900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-189500</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>82400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-53700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>39900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>120100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>33000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-87900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>49100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>131600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>49100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>131600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>101800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-82300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>45300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>120600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>82100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>30100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>13700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>84700</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-699400</v>
+      </c>
+      <c r="E102" s="3">
         <v>125000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-311800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>522400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>715300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-847200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-143700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>446200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-143700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>446200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>869600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-732700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>70000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>148000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>205600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-555400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-298000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>295200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>556500</v>
       </c>
     </row>
